--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A99D910-B8B6-4E4B-A2FF-61A09B0D3CE9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C63FE8-2C4E-4B4E-A85F-CDACB1C00C67}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -413,6 +413,9 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -422,9 +425,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -773,7 +773,7 @@
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="44" customWidth="1"/>
+    <col min="6" max="6" width="15" style="41" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
     <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
@@ -974,13 +974,13 @@
       <c r="B10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1007,7 +1007,9 @@
         <v>15.75</v>
       </c>
       <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="F11" s="38">
+        <v>1356</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1032,10 +1034,10 @@
         <v>322724</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="42">
+      <c r="E12" s="39">
         <v>928.5</v>
       </c>
-      <c r="F12" s="42"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="11"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1107,7 +1109,7 @@
       <c r="C15" s="12"/>
       <c r="D15" s="15"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="43"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="34"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1152,13 +1154,13 @@
       <c r="B17" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1253,7 +1255,7 @@
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="35"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1277,7 +1279,7 @@
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="35"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1322,13 +1324,13 @@
       <c r="B24" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -1423,7 +1425,7 @@
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="35"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1447,7 +1449,7 @@
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="34"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1492,13 +1494,13 @@
       <c r="B31" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -1593,7 +1595,7 @@
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="43"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="35"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1617,7 +1619,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="43"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="35"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1641,7 +1643,7 @@
       <c r="C37" s="27"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="43"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="34"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1662,13 +1664,13 @@
       <c r="B38" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -1792,7 +1794,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>0</v>
+        <v>1356</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5209,7 +5211,7 @@
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="44" customWidth="1"/>
+    <col min="6" max="6" width="15" style="41" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
     <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
@@ -5410,13 +5412,13 @@
       <c r="B10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -5443,7 +5445,9 @@
         <v>624</v>
       </c>
       <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="F11" s="38">
+        <v>1380</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -5471,7 +5475,7 @@
         <v>142</v>
       </c>
       <c r="E12" s="13"/>
-      <c r="F12" s="42">
+      <c r="F12" s="39">
         <v>732</v>
       </c>
       <c r="G12" s="11"/>
@@ -5545,7 +5549,7 @@
       <c r="C15" s="12"/>
       <c r="D15" s="15"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="43"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="34"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -5590,13 +5594,13 @@
       <c r="B17" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -5691,7 +5695,7 @@
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="35"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5715,7 +5719,7 @@
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="35"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5760,13 +5764,13 @@
       <c r="B24" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -5861,7 +5865,7 @@
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="35"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -5885,7 +5889,7 @@
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="34"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -5930,13 +5934,13 @@
       <c r="B31" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -6031,7 +6035,7 @@
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="43"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="35"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6055,7 +6059,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="43"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="35"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6079,7 +6083,7 @@
       <c r="C37" s="27"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="43"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="34"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6100,13 +6104,13 @@
       <c r="B38" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>732</v>
+        <v>2112</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -9647,7 +9651,7 @@
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="44" customWidth="1"/>
+    <col min="6" max="6" width="15" style="41" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
     <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
@@ -9848,13 +9852,13 @@
       <c r="B10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -9881,8 +9885,12 @@
       <c r="E11" s="38">
         <v>107</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="38">
+        <v>690</v>
+      </c>
+      <c r="G11" s="38">
+        <v>50</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -9906,10 +9914,10 @@
         <v>273403</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="42">
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="39">
         <v>918</v>
       </c>
       <c r="G12" s="11"/>
@@ -9983,7 +9991,7 @@
       <c r="C15" s="12"/>
       <c r="D15" s="15"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="43"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="34"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -10028,13 +10036,13 @@
       <c r="B17" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -10129,7 +10137,7 @@
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="35"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -10153,7 +10161,7 @@
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="35"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -10198,13 +10206,13 @@
       <c r="B24" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -10299,7 +10307,7 @@
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="35"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -10323,7 +10331,7 @@
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="34"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -10368,13 +10376,13 @@
       <c r="B31" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -10469,7 +10477,7 @@
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="43"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="35"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -10493,7 +10501,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="43"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="35"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -10517,7 +10525,7 @@
       <c r="C37" s="27"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="43"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="34"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -10538,13 +10546,13 @@
       <c r="B38" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -10668,11 +10676,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>918</v>
+        <v>1608</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C63FE8-2C4E-4B4E-A85F-CDACB1C00C67}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B85CCB-7C2D-4D3F-84FE-70938203F1EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1058,10 +1058,16 @@
       <c r="B13" s="31">
         <v>46085</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="36"/>
+      <c r="C13" s="37">
+        <v>387395</v>
+      </c>
+      <c r="D13" s="36">
+        <v>836.75</v>
+      </c>
       <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="37">
+        <v>2004</v>
+      </c>
       <c r="G13" s="36"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1782,11 +1788,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>588606</v>
+        <v>976001</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>15.75</v>
+        <v>852.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1794,7 +1800,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>1356</v>
+        <v>3360</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5498,11 +5504,19 @@
       <c r="B13" s="31">
         <v>46085</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="36"/>
+      <c r="C13" s="37">
+        <v>253739</v>
+      </c>
+      <c r="D13" s="36">
+        <v>44</v>
+      </c>
       <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="F13" s="37">
+        <v>1944</v>
+      </c>
+      <c r="G13" s="37">
+        <v>50</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -6222,11 +6236,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>542482.5</v>
+        <v>796221.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>766</v>
+        <v>810</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6234,11 +6248,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2112</v>
+        <v>4056</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -9940,11 +9954,19 @@
       <c r="B13" s="31">
         <v>46085</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="36"/>
+      <c r="C13" s="37">
+        <v>236285</v>
+      </c>
+      <c r="D13" s="36">
+        <v>67.75</v>
+      </c>
       <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="F13" s="37">
+        <v>1158</v>
+      </c>
+      <c r="G13" s="37">
+        <v>50</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -10664,11 +10686,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>533009</v>
+        <v>769294</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>0</v>
+        <v>67.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10676,11 +10698,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>1608</v>
+        <v>2766</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B85CCB-7C2D-4D3F-84FE-70938203F1EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC25C542-F625-43FE-B4C4-E83537681F50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
   <si>
     <t>SALES</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>NO TRIP</t>
   </si>
 </sst>
 </file>
@@ -1088,10 +1091,16 @@
       <c r="B14" s="31">
         <v>46086</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="12">
+        <v>301631</v>
+      </c>
+      <c r="D14" s="13">
+        <v>91.5</v>
+      </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="12">
+        <v>1950</v>
+      </c>
       <c r="G14" s="36"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1788,11 +1797,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>976001</v>
+        <v>1277632</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>852.5</v>
+        <v>944</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1800,7 +1809,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3360</v>
+        <v>5310</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5536,10 +5545,16 @@
       <c r="B14" s="31">
         <v>46086</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="12">
+        <v>264640</v>
+      </c>
+      <c r="D14" s="13">
+        <v>3553</v>
+      </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="12">
+        <v>1182</v>
+      </c>
       <c r="G14" s="36"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -6236,11 +6251,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>796221.5</v>
+        <v>1060861.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>810</v>
+        <v>4363</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6248,7 +6263,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>4056</v>
+        <v>5238</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -9986,11 +10001,13 @@
       <c r="B14" s="31">
         <v>46086</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="36"/>
+      <c r="C14" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -14093,12 +14110,13 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC25C542-F625-43FE-B4C4-E83537681F50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCD4229-958D-4330-B8B1-6CE20046D15B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="19">
   <si>
     <t>SALES</t>
   </si>
@@ -1121,11 +1121,13 @@
       <c r="B15" s="31">
         <v>46087</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="34"/>
+      <c r="C15" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -5204,12 +5206,13 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5575,11 +5578,13 @@
       <c r="B15" s="31">
         <v>46087</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="34"/>
+      <c r="C15" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -9658,12 +9663,13 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10027,11 +10033,20 @@
       <c r="B15" s="31">
         <v>46087</v>
       </c>
-      <c r="C15" s="12"/>
+      <c r="C15" s="12">
+        <v>363462</v>
+      </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="34"/>
+      <c r="E15" s="12">
+        <v>393</v>
+      </c>
+      <c r="F15" s="40">
+        <f>2472</f>
+        <v>2472</v>
+      </c>
+      <c r="G15" s="34">
+        <v>50</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -10703,7 +10718,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>769294</v>
+        <v>1132756</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10711,15 +10726,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>108.5</v>
+        <v>501.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2766</v>
+        <v>5238</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCD4229-958D-4330-B8B1-6CE20046D15B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F655CE77-2A92-433F-86A4-A1A6A082E3FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1147,8 +1147,12 @@
       <c r="B16" s="31">
         <v>46088</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="36"/>
+      <c r="C16" s="37">
+        <v>319434</v>
+      </c>
+      <c r="D16" s="36">
+        <v>1647.25</v>
+      </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
@@ -1799,11 +1803,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1277632</v>
+        <v>1597066</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>944</v>
+        <v>2591.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5604,10 +5608,16 @@
       <c r="B16" s="31">
         <v>46088</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="36"/>
+      <c r="C16" s="37">
+        <v>351657</v>
+      </c>
+      <c r="D16" s="36">
+        <v>12</v>
+      </c>
       <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="F16" s="36">
+        <v>1200</v>
+      </c>
       <c r="G16" s="36"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -6256,11 +6266,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1060861.5</v>
+        <v>1412518.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>4363</v>
+        <v>4375</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6268,7 +6278,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>5238</v>
+        <v>6438</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10066,10 +10076,16 @@
       <c r="B16" s="31">
         <v>46088</v>
       </c>
-      <c r="C16" s="37"/>
+      <c r="C16" s="37">
+        <v>412474</v>
+      </c>
       <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="37">
+        <v>1346.5</v>
+      </c>
+      <c r="F16" s="37">
+        <v>2736</v>
+      </c>
       <c r="G16" s="36"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -10718,7 +10734,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1132756</v>
+        <v>1545230</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10726,11 +10742,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>501.5</v>
+        <v>1848</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>5238</v>
+        <v>7974</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F655CE77-2A92-433F-86A4-A1A6A082E3FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7469D2E-9B0D-4D16-8D1B-161AB8AC666C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -142,10 +147,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,10 +356,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -364,29 +369,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -399,33 +403,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -769,24 +772,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="41" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E1"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:18" ht="16.5">
+    </row>
+    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -808,7 +810,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -828,7 +830,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75">
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>16</v>
@@ -850,7 +852,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -872,7 +874,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>7</v>
@@ -894,7 +896,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>11</v>
@@ -916,7 +918,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="15">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -936,17 +938,17 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="15">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -970,20 +972,20 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -996,21 +998,21 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="15">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>265882</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <v>15.75</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="38">
+      <c r="E11" s="34"/>
+      <c r="F11" s="37">
         <v>1356</v>
       </c>
       <c r="G11" s="11"/>
@@ -1026,21 +1028,21 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
         <v>322724</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="39">
+      <c r="E12" s="38">
         <v>928.5</v>
       </c>
-      <c r="F12" s="39"/>
+      <c r="F12" s="38"/>
       <c r="G12" s="11"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1054,24 +1056,24 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46085</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>387395</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>836.75</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37">
+      <c r="E13" s="35"/>
+      <c r="F13" s="36">
         <v>2004</v>
       </c>
-      <c r="G13" s="36"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1084,11 +1086,11 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46086</v>
       </c>
       <c r="C14" s="12">
@@ -1101,7 +1103,7 @@
       <c r="F14" s="12">
         <v>1950</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1114,20 +1116,20 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46087</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1140,22 +1142,22 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46088</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>319434</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <v>1647.25</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1168,20 +1170,20 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="15">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1194,17 +1196,24 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="15">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46090</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="12">
+        <v>529181</v>
+      </c>
+      <c r="D18" s="15">
+        <v>659.25</v>
+      </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12">
+        <f>3204</f>
+        <v>3204</v>
+      </c>
       <c r="G18" s="11"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1218,17 +1227,17 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46091</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="11"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1242,18 +1251,18 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" ht="15">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1266,18 +1275,18 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="15">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46093</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1290,18 +1299,18 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="15">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46094</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1314,18 +1323,18 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" ht="15">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -1338,20 +1347,20 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" ht="15">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -1364,11 +1373,11 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" ht="15">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46097</v>
       </c>
       <c r="C25" s="12"/>
@@ -1388,17 +1397,17 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" ht="15">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46098</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1412,17 +1421,17 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" ht="15">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46099</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="11"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1436,18 +1445,18 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" ht="15">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46100</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="35"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="34"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -1460,18 +1469,18 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" ht="15">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46101</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="34"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -1484,18 +1493,18 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" ht="15">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -1508,20 +1517,20 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" ht="15">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -1534,11 +1543,11 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" ht="15">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46104</v>
       </c>
       <c r="C32" s="12"/>
@@ -1558,17 +1567,17 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" ht="15">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46105</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1582,18 +1591,18 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" ht="15">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -1606,18 +1615,18 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" ht="15">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46107</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="35"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -1630,18 +1639,18 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" ht="15">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46108</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="35"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -1654,18 +1663,18 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" ht="15">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46109</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="34"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -1678,20 +1687,20 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" ht="15">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -1704,11 +1713,11 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" ht="15">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="30">
         <v>46111</v>
       </c>
       <c r="C39" s="12"/>
@@ -1728,11 +1737,11 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" ht="15">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -1752,15 +1761,15 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" ht="15">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1774,11 +1783,11 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" ht="15">
-      <c r="A42" s="24">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -1796,18 +1805,18 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="29" t="s">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1597066</v>
-      </c>
-      <c r="D43" s="32">
+        <v>2126247</v>
+      </c>
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>2591.25</v>
+        <v>3250.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1815,7 +1824,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>5310</v>
+        <v>8514</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -1833,14 +1842,14 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" ht="15">
-      <c r="A44" s="22"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="22"/>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="19"/>
@@ -1853,7 +1862,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" ht="15">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1873,7 +1882,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="15">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1893,7 +1902,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" ht="15">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1913,7 +1922,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" ht="15">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1933,7 +1942,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" ht="15">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1953,7 +1962,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" ht="15">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1973,7 +1982,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" ht="15">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1993,7 +2002,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" ht="15">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2013,7 +2022,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" ht="15">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2033,7 +2042,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" ht="15">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2053,7 +2062,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" ht="15">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2073,7 +2082,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" ht="15">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2093,7 +2102,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" ht="15">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2113,7 +2122,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" ht="15">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2133,7 +2142,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" ht="15">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2153,7 +2162,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" ht="15">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2173,7 +2182,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" ht="15">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2193,7 +2202,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" ht="15">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2213,7 +2222,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" ht="15">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2233,7 +2242,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" ht="15">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2253,7 +2262,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" ht="15">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2273,7 +2282,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" ht="15">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2293,7 +2302,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" ht="15">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2313,7 +2322,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" ht="15">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2333,7 +2342,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" ht="15">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2353,7 +2362,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" ht="15">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2373,7 +2382,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" ht="15">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2393,7 +2402,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" ht="15">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2413,7 +2422,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" ht="15">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2433,7 +2442,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" ht="15">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2453,7 +2462,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" ht="15">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2473,7 +2482,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" ht="15">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2493,7 +2502,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" ht="15">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2513,7 +2522,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" ht="15">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2533,7 +2542,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" ht="15">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2553,7 +2562,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" ht="15">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2573,7 +2582,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" ht="15">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2593,7 +2602,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" ht="15">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2613,7 +2622,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" ht="15">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2633,7 +2642,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" ht="15">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2653,7 +2662,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" ht="15">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2673,7 +2682,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" ht="15">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2693,7 +2702,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" ht="15">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2713,7 +2722,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" ht="15">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2733,7 +2742,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" ht="15">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2753,7 +2762,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" ht="15">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2773,7 +2782,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" ht="15">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2793,7 +2802,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" ht="15">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2813,7 +2822,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" ht="15">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2833,7 +2842,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" ht="15">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2853,7 +2862,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" ht="15">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -2873,7 +2882,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" ht="15">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -2893,7 +2902,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" ht="15">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -2913,7 +2922,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" ht="15">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -2933,7 +2942,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" ht="15">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -2953,7 +2962,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" ht="15">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -2973,7 +2982,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" ht="15">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -2993,7 +3002,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" ht="15">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3013,7 +3022,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" ht="15">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3033,7 +3042,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" ht="15">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3053,7 +3062,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" ht="15">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3073,7 +3082,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" ht="15">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3093,7 +3102,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" ht="15">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3113,7 +3122,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" ht="15">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3133,7 +3142,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" ht="15">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3153,7 +3162,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" ht="15">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3173,7 +3182,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" ht="15">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3193,7 +3202,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" ht="15">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3213,7 +3222,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" ht="15">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3233,7 +3242,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" ht="15">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3253,7 +3262,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" ht="15">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3273,7 +3282,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" ht="15">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3293,7 +3302,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" ht="15">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3313,7 +3322,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" ht="15">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3333,7 +3342,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" ht="15">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3353,7 +3362,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" ht="15">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3373,7 +3382,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" ht="15">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3393,7 +3402,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" ht="15">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3413,7 +3422,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" ht="15">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3433,7 +3442,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" ht="15">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3453,7 +3462,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" ht="15">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3473,7 +3482,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" ht="15">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3493,7 +3502,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" ht="15">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3513,7 +3522,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" ht="15">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3533,7 +3542,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" ht="15">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3553,7 +3562,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" ht="15">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -3573,7 +3582,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" ht="15">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -3593,7 +3602,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" ht="15">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -3613,7 +3622,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" ht="15">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -3633,7 +3642,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" ht="15">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -3653,7 +3662,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" ht="15">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -3673,7 +3682,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" ht="15">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -3693,7 +3702,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" ht="15">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -3713,7 +3722,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" ht="15">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -3733,7 +3742,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" ht="15">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -3753,7 +3762,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" ht="15">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -3773,7 +3782,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" ht="15">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -3793,7 +3802,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" ht="15">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -3813,7 +3822,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" ht="15">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -3833,7 +3842,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" ht="15">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -3853,7 +3862,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" ht="15">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -3873,7 +3882,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" ht="15">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -3893,7 +3902,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" ht="15">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -3913,7 +3922,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" ht="15">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -3933,7 +3942,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" ht="15">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -3953,7 +3962,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" ht="15">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -3973,7 +3982,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" ht="15">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -3993,7 +4002,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" ht="15">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4013,7 +4022,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" ht="15">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4033,7 +4042,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" ht="15">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4053,7 +4062,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" ht="15">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4073,7 +4082,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" ht="15">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4093,7 +4102,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" ht="15">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4113,7 +4122,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" ht="15">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4133,7 +4142,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" ht="15">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4153,7 +4162,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" ht="15">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4173,7 +4182,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" ht="15">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4193,7 +4202,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" ht="15">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4213,7 +4222,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" ht="15">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4233,7 +4242,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" ht="15">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4253,7 +4262,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" ht="15">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4273,7 +4282,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" ht="15">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4293,7 +4302,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" ht="15">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4313,7 +4322,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" ht="15">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4333,7 +4342,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" ht="15">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4353,7 +4362,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" ht="15">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4373,7 +4382,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" ht="15">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4393,7 +4402,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" ht="15">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4413,7 +4422,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" ht="15">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4433,7 +4442,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" ht="15">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4453,7 +4462,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" ht="15">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4473,7 +4482,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" ht="15">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4493,7 +4502,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" ht="15">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4513,7 +4522,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" ht="15">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4533,7 +4542,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" ht="15">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4553,7 +4562,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" ht="15">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -4573,7 +4582,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" ht="15">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -4593,7 +4602,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" ht="15">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -4613,7 +4622,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" ht="15">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -4633,7 +4642,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" ht="15">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -4653,7 +4662,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" ht="15">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -4673,7 +4682,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" ht="15">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -4693,7 +4702,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" ht="15">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -4713,7 +4722,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" ht="15">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -4733,7 +4742,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" ht="15">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -4753,7 +4762,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" ht="15">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -4773,7 +4782,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" ht="15">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -4793,7 +4802,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" ht="15">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -4813,7 +4822,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" ht="15">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -4833,7 +4842,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" ht="15">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -4853,7 +4862,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" ht="15">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -4873,341 +4882,257 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E196"/>
-      <c r="F196"/>
-    </row>
-    <row r="197" spans="1:18">
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E197"/>
-      <c r="F197"/>
-    </row>
-    <row r="198" spans="1:18">
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E198"/>
-      <c r="F198"/>
-    </row>
-    <row r="199" spans="1:18">
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E199"/>
-      <c r="F199"/>
-    </row>
-    <row r="200" spans="1:18">
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E200"/>
-      <c r="F200"/>
-    </row>
-    <row r="201" spans="1:18">
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E201"/>
-      <c r="F201"/>
-    </row>
-    <row r="202" spans="1:18">
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E202"/>
-      <c r="F202"/>
-    </row>
-    <row r="203" spans="1:18">
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E203"/>
-      <c r="F203"/>
-    </row>
-    <row r="204" spans="1:18">
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E204"/>
-      <c r="F204"/>
-    </row>
-    <row r="205" spans="1:18">
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E205"/>
-      <c r="F205"/>
-    </row>
-    <row r="206" spans="1:18">
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E206"/>
-      <c r="F206"/>
-    </row>
-    <row r="207" spans="1:18">
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E207"/>
-      <c r="F207"/>
-    </row>
-    <row r="208" spans="1:18">
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E208"/>
-      <c r="F208"/>
-    </row>
-    <row r="209" spans="5:6">
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E209"/>
-      <c r="F209"/>
-    </row>
-    <row r="210" spans="5:6">
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E210"/>
-      <c r="F210"/>
-    </row>
-    <row r="211" spans="5:6">
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E211"/>
-      <c r="F211"/>
-    </row>
-    <row r="212" spans="5:6">
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E212"/>
-      <c r="F212"/>
-    </row>
-    <row r="213" spans="5:6">
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E213"/>
-      <c r="F213"/>
-    </row>
-    <row r="214" spans="5:6">
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E214"/>
-      <c r="F214"/>
-    </row>
-    <row r="215" spans="5:6">
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E215"/>
-      <c r="F215"/>
-    </row>
-    <row r="216" spans="5:6">
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E216"/>
-      <c r="F216"/>
-    </row>
-    <row r="217" spans="5:6">
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E217"/>
-      <c r="F217"/>
-    </row>
-    <row r="218" spans="5:6">
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E218"/>
-      <c r="F218"/>
-    </row>
-    <row r="219" spans="5:6">
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E219"/>
-      <c r="F219"/>
-    </row>
-    <row r="220" spans="5:6">
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E220"/>
-      <c r="F220"/>
-    </row>
-    <row r="221" spans="5:6">
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E221"/>
-      <c r="F221"/>
-    </row>
-    <row r="222" spans="5:6">
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E222"/>
-      <c r="F222"/>
-    </row>
-    <row r="223" spans="5:6">
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E223"/>
-      <c r="F223"/>
-    </row>
-    <row r="224" spans="5:6">
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E224"/>
-      <c r="F224"/>
-    </row>
-    <row r="225" spans="5:6">
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E225"/>
-      <c r="F225"/>
-    </row>
-    <row r="226" spans="5:6">
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E226"/>
-      <c r="F226"/>
-    </row>
-    <row r="227" spans="5:6">
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E227"/>
-      <c r="F227"/>
-    </row>
-    <row r="228" spans="5:6">
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E228"/>
-      <c r="F228"/>
-    </row>
-    <row r="229" spans="5:6">
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E229"/>
-      <c r="F229"/>
-    </row>
-    <row r="230" spans="5:6">
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E230"/>
-      <c r="F230"/>
-    </row>
-    <row r="231" spans="5:6">
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E231"/>
-      <c r="F231"/>
-    </row>
-    <row r="232" spans="5:6">
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E232"/>
-      <c r="F232"/>
-    </row>
-    <row r="233" spans="5:6">
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E233"/>
-      <c r="F233"/>
-    </row>
-    <row r="234" spans="5:6">
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E234"/>
-      <c r="F234"/>
-    </row>
-    <row r="235" spans="5:6">
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E235"/>
-      <c r="F235"/>
-    </row>
-    <row r="236" spans="5:6">
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E236"/>
-      <c r="F236"/>
-    </row>
-    <row r="237" spans="5:6">
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E237"/>
-      <c r="F237"/>
-    </row>
-    <row r="238" spans="5:6">
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E238"/>
-      <c r="F238"/>
-    </row>
-    <row r="239" spans="5:6">
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E239"/>
-      <c r="F239"/>
-    </row>
-    <row r="240" spans="5:6">
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E240"/>
-      <c r="F240"/>
-    </row>
-    <row r="241" spans="5:6">
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E241"/>
-      <c r="F241"/>
-    </row>
-    <row r="242" spans="5:6">
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E242"/>
-      <c r="F242"/>
-    </row>
-    <row r="243" spans="5:6">
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E243"/>
-      <c r="F243"/>
-    </row>
-    <row r="244" spans="5:6">
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E244"/>
-      <c r="F244"/>
-    </row>
-    <row r="245" spans="5:6">
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E245"/>
-      <c r="F245"/>
-    </row>
-    <row r="246" spans="5:6">
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E246"/>
-      <c r="F246"/>
-    </row>
-    <row r="247" spans="5:6">
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E247"/>
-      <c r="F247"/>
-    </row>
-    <row r="248" spans="5:6">
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E248"/>
-      <c r="F248"/>
-    </row>
-    <row r="249" spans="5:6">
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E249"/>
-      <c r="F249"/>
-    </row>
-    <row r="250" spans="5:6">
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E250"/>
-      <c r="F250"/>
-    </row>
-    <row r="251" spans="5:6">
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E251"/>
-      <c r="F251"/>
-    </row>
-    <row r="252" spans="5:6">
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E252"/>
-      <c r="F252"/>
-    </row>
-    <row r="253" spans="5:6">
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E253"/>
-      <c r="F253"/>
-    </row>
-    <row r="254" spans="5:6">
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E254"/>
-      <c r="F254"/>
-    </row>
-    <row r="255" spans="5:6">
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E255"/>
-      <c r="F255"/>
-    </row>
-    <row r="256" spans="5:6">
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E256"/>
-      <c r="F256"/>
-    </row>
-    <row r="257" spans="5:6">
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E257"/>
-      <c r="F257"/>
-    </row>
-    <row r="258" spans="5:6">
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E258"/>
-      <c r="F258"/>
-    </row>
-    <row r="259" spans="5:6">
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E259"/>
-      <c r="F259"/>
-    </row>
-    <row r="260" spans="5:6">
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E260"/>
-      <c r="F260"/>
-    </row>
-    <row r="261" spans="5:6">
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E261"/>
-      <c r="F261"/>
-    </row>
-    <row r="262" spans="5:6">
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E262"/>
-      <c r="F262"/>
-    </row>
-    <row r="263" spans="5:6">
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E263"/>
-      <c r="F263"/>
-    </row>
-    <row r="264" spans="5:6">
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E264"/>
-      <c r="F264"/>
-    </row>
-    <row r="265" spans="5:6">
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E265"/>
-      <c r="F265"/>
-    </row>
-    <row r="266" spans="5:6">
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E266"/>
-      <c r="F266"/>
-    </row>
-    <row r="267" spans="5:6">
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E267"/>
-      <c r="F267"/>
-    </row>
-    <row r="268" spans="5:6">
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E268"/>
-      <c r="F268"/>
-    </row>
-    <row r="269" spans="5:6">
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E269"/>
-      <c r="F269"/>
-    </row>
-    <row r="270" spans="5:6">
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E270"/>
-      <c r="F270"/>
-    </row>
-    <row r="271" spans="5:6">
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E271"/>
-      <c r="F271"/>
-    </row>
-    <row r="272" spans="5:6">
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E272"/>
-      <c r="F272"/>
-    </row>
-    <row r="273" spans="5:6">
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E273"/>
-      <c r="F273"/>
-    </row>
-    <row r="274" spans="5:6">
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E274"/>
-      <c r="F274"/>
-    </row>
-    <row r="275" spans="5:6">
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E275"/>
-      <c r="F275"/>
-    </row>
-    <row r="276" spans="5:6">
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E276"/>
-      <c r="F276"/>
-    </row>
-    <row r="277" spans="5:6">
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E277"/>
-      <c r="F277"/>
-    </row>
-    <row r="278" spans="5:6">
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E278"/>
-      <c r="F278"/>
-    </row>
-    <row r="279" spans="5:6">
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E279"/>
-      <c r="F279"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5226,24 +5151,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E574FF03-14F0-421D-8F76-5519CF1A2460}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="41" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E1"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:18" ht="16.5">
+    </row>
+    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -5265,7 +5189,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5285,7 +5209,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75">
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>15</v>
@@ -5307,7 +5231,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -5329,7 +5253,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -5351,7 +5275,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>14</v>
@@ -5373,7 +5297,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="15">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -5393,17 +5317,17 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="15">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -5427,20 +5351,20 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -5453,21 +5377,21 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="15">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>313708.5</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <v>624</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="38">
+      <c r="E11" s="34"/>
+      <c r="F11" s="37">
         <v>1380</v>
       </c>
       <c r="G11" s="11"/>
@@ -5483,11 +5407,11 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
@@ -5497,7 +5421,7 @@
         <v>142</v>
       </c>
       <c r="E12" s="13"/>
-      <c r="F12" s="39">
+      <c r="F12" s="38">
         <v>732</v>
       </c>
       <c r="G12" s="11"/>
@@ -5513,24 +5437,24 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46085</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>253739</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>44</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37">
+      <c r="E13" s="35"/>
+      <c r="F13" s="36">
         <v>1944</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>50</v>
       </c>
       <c r="H13" s="1"/>
@@ -5545,11 +5469,11 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46086</v>
       </c>
       <c r="C14" s="12">
@@ -5562,7 +5486,7 @@
       <c r="F14" s="12">
         <v>1182</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -5575,20 +5499,20 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46087</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -5601,24 +5525,24 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46088</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>351657</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <v>12</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36">
+      <c r="E16" s="35"/>
+      <c r="F16" s="35">
         <v>1200</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -5631,20 +5555,20 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="15">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -5657,17 +5581,23 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="15">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46090</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="12">
+        <v>502921</v>
+      </c>
+      <c r="D18" s="15">
+        <v>197.5</v>
+      </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12">
+        <v>3372</v>
+      </c>
       <c r="G18" s="11"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5681,17 +5611,17 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46091</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="11"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5705,18 +5635,18 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" ht="15">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -5729,18 +5659,18 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="15">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46093</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -5753,18 +5683,18 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="15">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46094</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5777,18 +5707,18 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" ht="15">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -5801,20 +5731,20 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" ht="15">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -5827,11 +5757,11 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" ht="15">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46097</v>
       </c>
       <c r="C25" s="12"/>
@@ -5851,17 +5781,17 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" ht="15">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46098</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -5875,17 +5805,17 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" ht="15">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46099</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="11"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -5899,18 +5829,18 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" ht="15">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46100</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="35"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="34"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -5923,18 +5853,18 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" ht="15">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46101</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="34"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -5947,18 +5877,18 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" ht="15">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -5971,20 +5901,20 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" ht="15">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -5997,11 +5927,11 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" ht="15">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46104</v>
       </c>
       <c r="C32" s="12"/>
@@ -6021,17 +5951,17 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" ht="15">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46105</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6045,18 +5975,18 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" ht="15">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -6069,18 +5999,18 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" ht="15">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46107</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="35"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -6093,18 +6023,18 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" ht="15">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46108</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="35"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -6117,18 +6047,18 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" ht="15">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46109</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="34"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -6141,20 +6071,20 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" ht="15">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -6167,11 +6097,11 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" ht="15">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="30">
         <v>46111</v>
       </c>
       <c r="C39" s="12"/>
@@ -6191,11 +6121,11 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" ht="15">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -6215,15 +6145,15 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" ht="15">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -6237,11 +6167,11 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" ht="15">
-      <c r="A42" s="24">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -6259,18 +6189,18 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="29" t="s">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1412518.5</v>
-      </c>
-      <c r="D43" s="32">
+        <v>1915439.5</v>
+      </c>
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>4375</v>
+        <v>4572.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6278,7 +6208,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>6438</v>
+        <v>9810</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -6296,14 +6226,14 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" ht="15">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="22"/>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="19"/>
@@ -6316,7 +6246,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" ht="15">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -6336,7 +6266,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="15">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -6356,7 +6286,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" ht="15">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -6376,7 +6306,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" ht="15">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -6396,7 +6326,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" ht="15">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -6416,7 +6346,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" ht="15">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -6436,7 +6366,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" ht="15">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -6456,7 +6386,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" ht="15">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -6476,7 +6406,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" ht="15">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -6496,7 +6426,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" ht="15">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -6516,7 +6446,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" ht="15">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -6536,7 +6466,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" ht="15">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -6556,7 +6486,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" ht="15">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -6576,7 +6506,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" ht="15">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -6596,7 +6526,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" ht="15">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -6616,7 +6546,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" ht="15">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -6636,7 +6566,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" ht="15">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -6656,7 +6586,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" ht="15">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -6676,7 +6606,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" ht="15">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6696,7 +6626,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" ht="15">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6716,7 +6646,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" ht="15">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -6736,7 +6666,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" ht="15">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -6756,7 +6686,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" ht="15">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -6776,7 +6706,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" ht="15">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6796,7 +6726,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" ht="15">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6816,7 +6746,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" ht="15">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6836,7 +6766,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" ht="15">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -6856,7 +6786,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" ht="15">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -6876,7 +6806,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" ht="15">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -6896,7 +6826,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" ht="15">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6916,7 +6846,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" ht="15">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6936,7 +6866,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" ht="15">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6956,7 +6886,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" ht="15">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6976,7 +6906,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" ht="15">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6996,7 +6926,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" ht="15">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -7016,7 +6946,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" ht="15">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -7036,7 +6966,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" ht="15">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7056,7 +6986,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" ht="15">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7076,7 +7006,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" ht="15">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7096,7 +7026,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" ht="15">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7116,7 +7046,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" ht="15">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7136,7 +7066,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" ht="15">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7156,7 +7086,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" ht="15">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7176,7 +7106,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" ht="15">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7196,7 +7126,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" ht="15">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7216,7 +7146,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" ht="15">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7236,7 +7166,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" ht="15">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7256,7 +7186,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" ht="15">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7276,7 +7206,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" ht="15">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7296,7 +7226,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" ht="15">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7316,7 +7246,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" ht="15">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7336,7 +7266,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" ht="15">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7356,7 +7286,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" ht="15">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7376,7 +7306,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" ht="15">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7396,7 +7326,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" ht="15">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7416,7 +7346,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" ht="15">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7436,7 +7366,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" ht="15">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7456,7 +7386,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" ht="15">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7476,7 +7406,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" ht="15">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7496,7 +7426,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" ht="15">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7516,7 +7446,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" ht="15">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7536,7 +7466,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" ht="15">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7556,7 +7486,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" ht="15">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7576,7 +7506,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" ht="15">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7596,7 +7526,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" ht="15">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7616,7 +7546,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" ht="15">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7636,7 +7566,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" ht="15">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7656,7 +7586,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" ht="15">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7676,7 +7606,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" ht="15">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7696,7 +7626,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" ht="15">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7716,7 +7646,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" ht="15">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7736,7 +7666,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" ht="15">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7756,7 +7686,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" ht="15">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7776,7 +7706,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" ht="15">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7796,7 +7726,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" ht="15">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7816,7 +7746,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" ht="15">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7836,7 +7766,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" ht="15">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7856,7 +7786,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" ht="15">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7876,7 +7806,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" ht="15">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7896,7 +7826,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" ht="15">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7916,7 +7846,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" ht="15">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -7936,7 +7866,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" ht="15">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7956,7 +7886,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" ht="15">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7976,7 +7906,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" ht="15">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7996,7 +7926,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" ht="15">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8016,7 +7946,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" ht="15">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8036,7 +7966,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" ht="15">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -8056,7 +7986,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" ht="15">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -8076,7 +8006,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" ht="15">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -8096,7 +8026,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" ht="15">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -8116,7 +8046,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" ht="15">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -8136,7 +8066,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" ht="15">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -8156,7 +8086,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" ht="15">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -8176,7 +8106,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" ht="15">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -8196,7 +8126,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" ht="15">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8216,7 +8146,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" ht="15">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -8236,7 +8166,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" ht="15">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -8256,7 +8186,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" ht="15">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -8276,7 +8206,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" ht="15">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -8296,7 +8226,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" ht="15">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -8316,7 +8246,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" ht="15">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -8336,7 +8266,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" ht="15">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -8356,7 +8286,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" ht="15">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -8376,7 +8306,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" ht="15">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -8396,7 +8326,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" ht="15">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -8416,7 +8346,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" ht="15">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -8436,7 +8366,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" ht="15">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -8456,7 +8386,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" ht="15">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -8476,7 +8406,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" ht="15">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -8496,7 +8426,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" ht="15">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -8516,7 +8446,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" ht="15">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -8536,7 +8466,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" ht="15">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -8556,7 +8486,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" ht="15">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -8576,7 +8506,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" ht="15">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -8596,7 +8526,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" ht="15">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -8616,7 +8546,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" ht="15">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -8636,7 +8566,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" ht="15">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -8656,7 +8586,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" ht="15">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8676,7 +8606,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" ht="15">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8696,7 +8626,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" ht="15">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -8716,7 +8646,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" ht="15">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -8736,7 +8666,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" ht="15">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -8756,7 +8686,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" ht="15">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -8776,7 +8706,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" ht="15">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8796,7 +8726,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" ht="15">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8816,7 +8746,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" ht="15">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8836,7 +8766,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" ht="15">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8856,7 +8786,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" ht="15">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8876,7 +8806,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" ht="15">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8896,7 +8826,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" ht="15">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8916,7 +8846,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" ht="15">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8936,7 +8866,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" ht="15">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8956,7 +8886,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" ht="15">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8976,7 +8906,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" ht="15">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8996,7 +8926,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" ht="15">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -9016,7 +8946,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" ht="15">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -9036,7 +8966,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" ht="15">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -9056,7 +8986,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" ht="15">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -9076,7 +9006,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" ht="15">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -9096,7 +9026,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" ht="15">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -9116,7 +9046,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" ht="15">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -9136,7 +9066,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" ht="15">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -9156,7 +9086,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" ht="15">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -9176,7 +9106,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" ht="15">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -9196,7 +9126,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" ht="15">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -9216,7 +9146,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" ht="15">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -9236,7 +9166,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" ht="15">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -9256,7 +9186,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" ht="15">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -9276,7 +9206,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" ht="15">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9296,7 +9226,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" ht="15">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9316,7 +9246,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" ht="15">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9336,341 +9266,257 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E196"/>
-      <c r="F196"/>
-    </row>
-    <row r="197" spans="1:18">
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E197"/>
-      <c r="F197"/>
-    </row>
-    <row r="198" spans="1:18">
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E198"/>
-      <c r="F198"/>
-    </row>
-    <row r="199" spans="1:18">
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E199"/>
-      <c r="F199"/>
-    </row>
-    <row r="200" spans="1:18">
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E200"/>
-      <c r="F200"/>
-    </row>
-    <row r="201" spans="1:18">
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E201"/>
-      <c r="F201"/>
-    </row>
-    <row r="202" spans="1:18">
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E202"/>
-      <c r="F202"/>
-    </row>
-    <row r="203" spans="1:18">
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E203"/>
-      <c r="F203"/>
-    </row>
-    <row r="204" spans="1:18">
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E204"/>
-      <c r="F204"/>
-    </row>
-    <row r="205" spans="1:18">
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E205"/>
-      <c r="F205"/>
-    </row>
-    <row r="206" spans="1:18">
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E206"/>
-      <c r="F206"/>
-    </row>
-    <row r="207" spans="1:18">
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E207"/>
-      <c r="F207"/>
-    </row>
-    <row r="208" spans="1:18">
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E208"/>
-      <c r="F208"/>
-    </row>
-    <row r="209" spans="5:6">
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E209"/>
-      <c r="F209"/>
-    </row>
-    <row r="210" spans="5:6">
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E210"/>
-      <c r="F210"/>
-    </row>
-    <row r="211" spans="5:6">
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E211"/>
-      <c r="F211"/>
-    </row>
-    <row r="212" spans="5:6">
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E212"/>
-      <c r="F212"/>
-    </row>
-    <row r="213" spans="5:6">
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E213"/>
-      <c r="F213"/>
-    </row>
-    <row r="214" spans="5:6">
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E214"/>
-      <c r="F214"/>
-    </row>
-    <row r="215" spans="5:6">
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E215"/>
-      <c r="F215"/>
-    </row>
-    <row r="216" spans="5:6">
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E216"/>
-      <c r="F216"/>
-    </row>
-    <row r="217" spans="5:6">
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E217"/>
-      <c r="F217"/>
-    </row>
-    <row r="218" spans="5:6">
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E218"/>
-      <c r="F218"/>
-    </row>
-    <row r="219" spans="5:6">
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E219"/>
-      <c r="F219"/>
-    </row>
-    <row r="220" spans="5:6">
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E220"/>
-      <c r="F220"/>
-    </row>
-    <row r="221" spans="5:6">
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E221"/>
-      <c r="F221"/>
-    </row>
-    <row r="222" spans="5:6">
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E222"/>
-      <c r="F222"/>
-    </row>
-    <row r="223" spans="5:6">
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E223"/>
-      <c r="F223"/>
-    </row>
-    <row r="224" spans="5:6">
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E224"/>
-      <c r="F224"/>
-    </row>
-    <row r="225" spans="5:6">
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E225"/>
-      <c r="F225"/>
-    </row>
-    <row r="226" spans="5:6">
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E226"/>
-      <c r="F226"/>
-    </row>
-    <row r="227" spans="5:6">
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E227"/>
-      <c r="F227"/>
-    </row>
-    <row r="228" spans="5:6">
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E228"/>
-      <c r="F228"/>
-    </row>
-    <row r="229" spans="5:6">
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E229"/>
-      <c r="F229"/>
-    </row>
-    <row r="230" spans="5:6">
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E230"/>
-      <c r="F230"/>
-    </row>
-    <row r="231" spans="5:6">
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E231"/>
-      <c r="F231"/>
-    </row>
-    <row r="232" spans="5:6">
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E232"/>
-      <c r="F232"/>
-    </row>
-    <row r="233" spans="5:6">
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E233"/>
-      <c r="F233"/>
-    </row>
-    <row r="234" spans="5:6">
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E234"/>
-      <c r="F234"/>
-    </row>
-    <row r="235" spans="5:6">
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E235"/>
-      <c r="F235"/>
-    </row>
-    <row r="236" spans="5:6">
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E236"/>
-      <c r="F236"/>
-    </row>
-    <row r="237" spans="5:6">
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E237"/>
-      <c r="F237"/>
-    </row>
-    <row r="238" spans="5:6">
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E238"/>
-      <c r="F238"/>
-    </row>
-    <row r="239" spans="5:6">
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E239"/>
-      <c r="F239"/>
-    </row>
-    <row r="240" spans="5:6">
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E240"/>
-      <c r="F240"/>
-    </row>
-    <row r="241" spans="5:6">
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E241"/>
-      <c r="F241"/>
-    </row>
-    <row r="242" spans="5:6">
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E242"/>
-      <c r="F242"/>
-    </row>
-    <row r="243" spans="5:6">
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E243"/>
-      <c r="F243"/>
-    </row>
-    <row r="244" spans="5:6">
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E244"/>
-      <c r="F244"/>
-    </row>
-    <row r="245" spans="5:6">
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E245"/>
-      <c r="F245"/>
-    </row>
-    <row r="246" spans="5:6">
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E246"/>
-      <c r="F246"/>
-    </row>
-    <row r="247" spans="5:6">
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E247"/>
-      <c r="F247"/>
-    </row>
-    <row r="248" spans="5:6">
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E248"/>
-      <c r="F248"/>
-    </row>
-    <row r="249" spans="5:6">
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E249"/>
-      <c r="F249"/>
-    </row>
-    <row r="250" spans="5:6">
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E250"/>
-      <c r="F250"/>
-    </row>
-    <row r="251" spans="5:6">
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E251"/>
-      <c r="F251"/>
-    </row>
-    <row r="252" spans="5:6">
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E252"/>
-      <c r="F252"/>
-    </row>
-    <row r="253" spans="5:6">
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E253"/>
-      <c r="F253"/>
-    </row>
-    <row r="254" spans="5:6">
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E254"/>
-      <c r="F254"/>
-    </row>
-    <row r="255" spans="5:6">
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E255"/>
-      <c r="F255"/>
-    </row>
-    <row r="256" spans="5:6">
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E256"/>
-      <c r="F256"/>
-    </row>
-    <row r="257" spans="5:6">
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E257"/>
-      <c r="F257"/>
-    </row>
-    <row r="258" spans="5:6">
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E258"/>
-      <c r="F258"/>
-    </row>
-    <row r="259" spans="5:6">
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E259"/>
-      <c r="F259"/>
-    </row>
-    <row r="260" spans="5:6">
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E260"/>
-      <c r="F260"/>
-    </row>
-    <row r="261" spans="5:6">
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E261"/>
-      <c r="F261"/>
-    </row>
-    <row r="262" spans="5:6">
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E262"/>
-      <c r="F262"/>
-    </row>
-    <row r="263" spans="5:6">
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E263"/>
-      <c r="F263"/>
-    </row>
-    <row r="264" spans="5:6">
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E264"/>
-      <c r="F264"/>
-    </row>
-    <row r="265" spans="5:6">
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E265"/>
-      <c r="F265"/>
-    </row>
-    <row r="266" spans="5:6">
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E266"/>
-      <c r="F266"/>
-    </row>
-    <row r="267" spans="5:6">
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E267"/>
-      <c r="F267"/>
-    </row>
-    <row r="268" spans="5:6">
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E268"/>
-      <c r="F268"/>
-    </row>
-    <row r="269" spans="5:6">
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E269"/>
-      <c r="F269"/>
-    </row>
-    <row r="270" spans="5:6">
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E270"/>
-      <c r="F270"/>
-    </row>
-    <row r="271" spans="5:6">
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E271"/>
-      <c r="F271"/>
-    </row>
-    <row r="272" spans="5:6">
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E272"/>
-      <c r="F272"/>
-    </row>
-    <row r="273" spans="5:6">
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E273"/>
-      <c r="F273"/>
-    </row>
-    <row r="274" spans="5:6">
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E274"/>
-      <c r="F274"/>
-    </row>
-    <row r="275" spans="5:6">
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E275"/>
-      <c r="F275"/>
-    </row>
-    <row r="276" spans="5:6">
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E276"/>
-      <c r="F276"/>
-    </row>
-    <row r="277" spans="5:6">
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E277"/>
-      <c r="F277"/>
-    </row>
-    <row r="278" spans="5:6">
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E278"/>
-      <c r="F278"/>
-    </row>
-    <row r="279" spans="5:6">
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E279"/>
-      <c r="F279"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -9689,24 +9535,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
-    <col min="6" max="6" width="15" style="41" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E1"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:18" ht="16.5">
+    </row>
+    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -9728,7 +9573,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -9748,7 +9593,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75">
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>15</v>
@@ -9770,7 +9615,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -9792,7 +9637,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>10</v>
@@ -9814,7 +9659,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>13</v>
@@ -9836,7 +9681,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="15">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -9856,17 +9701,17 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="15">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -9890,20 +9735,20 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -9916,24 +9761,24 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="15">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>259606</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="38">
+      <c r="D11" s="35"/>
+      <c r="E11" s="37">
         <v>107</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <v>690</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="37">
         <v>50</v>
       </c>
       <c r="H11" s="1"/>
@@ -9948,21 +9793,21 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
         <v>273403</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="39">
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="38">
         <v>918</v>
       </c>
       <c r="G12" s="11"/>
@@ -9978,24 +9823,24 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46085</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>236285</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>67.75</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37">
+      <c r="E13" s="35"/>
+      <c r="F13" s="36">
         <v>1158</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>50</v>
       </c>
       <c r="H13" s="1"/>
@@ -10010,20 +9855,20 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46086</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -10036,11 +9881,11 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46087</v>
       </c>
       <c r="C15" s="12">
@@ -10050,11 +9895,11 @@
       <c r="E15" s="12">
         <v>393</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="39">
         <f>2472</f>
         <v>2472</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="33">
         <v>50</v>
       </c>
       <c r="H15" s="1"/>
@@ -10069,24 +9914,24 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46088</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>412474</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37">
+      <c r="D16" s="35"/>
+      <c r="E16" s="36">
         <v>1346.5</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="36">
         <v>2736</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -10099,20 +9944,20 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="15">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -10125,17 +9970,23 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="15">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46090</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="12">
+        <v>344843</v>
+      </c>
+      <c r="D18" s="15">
+        <v>220.75</v>
+      </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12">
+        <v>300</v>
+      </c>
       <c r="G18" s="11"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -10149,17 +10000,17 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46091</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="11"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -10173,18 +10024,18 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" ht="15">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -10197,18 +10048,18 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="15">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46093</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -10221,18 +10072,18 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="15">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46094</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -10245,18 +10096,18 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" ht="15">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -10269,20 +10120,20 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" ht="15">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -10295,11 +10146,11 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" ht="15">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46097</v>
       </c>
       <c r="C25" s="12"/>
@@ -10319,17 +10170,17 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" ht="15">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46098</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -10343,17 +10194,17 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" ht="15">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46099</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="11"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -10367,18 +10218,18 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" ht="15">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46100</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="35"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="34"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -10391,18 +10242,18 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" ht="15">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46101</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="15"/>
       <c r="E29" s="12"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="34"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -10415,18 +10266,18 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" ht="15">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -10439,20 +10290,20 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" ht="15">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -10465,11 +10316,11 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" ht="15">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46104</v>
       </c>
       <c r="C32" s="12"/>
@@ -10489,17 +10340,17 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" ht="15">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46105</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -10513,18 +10364,18 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" ht="15">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -10537,18 +10388,18 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" ht="15">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46107</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="35"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -10561,18 +10412,18 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" ht="15">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46108</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="35"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -10585,18 +10436,18 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" ht="15">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46109</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="15"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="34"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -10609,20 +10460,20 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" ht="15">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -10635,11 +10486,11 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" ht="15">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="30">
         <v>46111</v>
       </c>
       <c r="C39" s="12"/>
@@ -10659,11 +10510,11 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" ht="15">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -10683,15 +10534,15 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" ht="15">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -10705,11 +10556,11 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" ht="15">
-      <c r="A42" s="24">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -10727,18 +10578,18 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="29" t="s">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1545230</v>
-      </c>
-      <c r="D43" s="32">
+        <v>1890073</v>
+      </c>
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>67.75</v>
+        <v>288.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10746,7 +10597,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>7974</v>
+        <v>8274</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10764,14 +10615,14 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" ht="15">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="22"/>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="19"/>
@@ -10784,7 +10635,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" ht="15">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -10804,7 +10655,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="15">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -10824,7 +10675,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" ht="15">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -10844,7 +10695,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" ht="15">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -10864,7 +10715,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" ht="15">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -10884,7 +10735,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" ht="15">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -10904,7 +10755,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" ht="15">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -10924,7 +10775,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" ht="15">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -10944,7 +10795,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" ht="15">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -10964,7 +10815,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" ht="15">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -10984,7 +10835,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" ht="15">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -11004,7 +10855,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" ht="15">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -11024,7 +10875,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" ht="15">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -11044,7 +10895,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" ht="15">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -11064,7 +10915,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" ht="15">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -11084,7 +10935,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" ht="15">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -11104,7 +10955,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" ht="15">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -11124,7 +10975,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" ht="15">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -11144,7 +10995,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" ht="15">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -11164,7 +11015,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" ht="15">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -11184,7 +11035,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" ht="15">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -11204,7 +11055,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" ht="15">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -11224,7 +11075,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" ht="15">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -11244,7 +11095,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" ht="15">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -11264,7 +11115,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" ht="15">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -11284,7 +11135,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" ht="15">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -11304,7 +11155,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" ht="15">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -11324,7 +11175,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" ht="15">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -11344,7 +11195,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" ht="15">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -11364,7 +11215,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" ht="15">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -11384,7 +11235,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" ht="15">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -11404,7 +11255,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" ht="15">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -11424,7 +11275,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" ht="15">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -11444,7 +11295,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" ht="15">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -11464,7 +11315,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" ht="15">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -11484,7 +11335,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" ht="15">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -11504,7 +11355,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" ht="15">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -11524,7 +11375,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" ht="15">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -11544,7 +11395,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" ht="15">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -11564,7 +11415,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" ht="15">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -11584,7 +11435,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" ht="15">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -11604,7 +11455,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" ht="15">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -11624,7 +11475,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" ht="15">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -11644,7 +11495,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" ht="15">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -11664,7 +11515,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" ht="15">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -11684,7 +11535,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" ht="15">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -11704,7 +11555,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" ht="15">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -11724,7 +11575,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" ht="15">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -11744,7 +11595,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" ht="15">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -11764,7 +11615,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" ht="15">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -11784,7 +11635,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" ht="15">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -11804,7 +11655,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" ht="15">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -11824,7 +11675,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" ht="15">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -11844,7 +11695,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" ht="15">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -11864,7 +11715,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" ht="15">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -11884,7 +11735,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" ht="15">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -11904,7 +11755,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" ht="15">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -11924,7 +11775,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" ht="15">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -11944,7 +11795,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" ht="15">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -11964,7 +11815,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" ht="15">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -11984,7 +11835,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" ht="15">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -12004,7 +11855,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" ht="15">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -12024,7 +11875,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" ht="15">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -12044,7 +11895,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" ht="15">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -12064,7 +11915,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" ht="15">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -12084,7 +11935,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" ht="15">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -12104,7 +11955,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" ht="15">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -12124,7 +11975,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" ht="15">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -12144,7 +11995,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" ht="15">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -12164,7 +12015,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" ht="15">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -12184,7 +12035,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" ht="15">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -12204,7 +12055,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" ht="15">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -12224,7 +12075,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" ht="15">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -12244,7 +12095,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" ht="15">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -12264,7 +12115,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" ht="15">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -12284,7 +12135,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" ht="15">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12304,7 +12155,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" ht="15">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12324,7 +12175,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" ht="15">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12344,7 +12195,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" ht="15">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12364,7 +12215,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" ht="15">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12384,7 +12235,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" ht="15">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -12404,7 +12255,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" ht="15">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -12424,7 +12275,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" ht="15">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -12444,7 +12295,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" ht="15">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -12464,7 +12315,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" ht="15">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -12484,7 +12335,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" ht="15">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -12504,7 +12355,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" ht="15">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -12524,7 +12375,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" ht="15">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -12544,7 +12395,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" ht="15">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -12564,7 +12415,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" ht="15">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -12584,7 +12435,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" ht="15">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -12604,7 +12455,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" ht="15">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -12624,7 +12475,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" ht="15">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -12644,7 +12495,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" ht="15">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -12664,7 +12515,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" ht="15">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -12684,7 +12535,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" ht="15">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -12704,7 +12555,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" ht="15">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -12724,7 +12575,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" ht="15">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -12744,7 +12595,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" ht="15">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -12764,7 +12615,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" ht="15">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -12784,7 +12635,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" ht="15">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -12804,7 +12655,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" ht="15">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -12824,7 +12675,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" ht="15">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -12844,7 +12695,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" ht="15">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -12864,7 +12715,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" ht="15">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -12884,7 +12735,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" ht="15">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -12904,7 +12755,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" ht="15">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -12924,7 +12775,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" ht="15">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -12944,7 +12795,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" ht="15">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -12964,7 +12815,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" ht="15">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -12984,7 +12835,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" ht="15">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -13004,7 +12855,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" ht="15">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -13024,7 +12875,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" ht="15">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -13044,7 +12895,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" ht="15">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -13064,7 +12915,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" ht="15">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -13084,7 +12935,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" ht="15">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -13104,7 +12955,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" ht="15">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -13124,7 +12975,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" ht="15">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -13144,7 +12995,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" ht="15">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -13164,7 +13015,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" ht="15">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -13184,7 +13035,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" ht="15">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -13204,7 +13055,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" ht="15">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -13224,7 +13075,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" ht="15">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -13244,7 +13095,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" ht="15">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -13264,7 +13115,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" ht="15">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -13284,7 +13135,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" ht="15">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -13304,7 +13155,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" ht="15">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -13324,7 +13175,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" ht="15">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -13344,7 +13195,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" ht="15">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -13364,7 +13215,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" ht="15">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -13384,7 +13235,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" ht="15">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -13404,7 +13255,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" ht="15">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -13424,7 +13275,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" ht="15">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -13444,7 +13295,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" ht="15">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -13464,7 +13315,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" ht="15">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -13484,7 +13335,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" ht="15">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -13504,7 +13355,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" ht="15">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -13524,7 +13375,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" ht="15">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -13544,7 +13395,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" ht="15">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -13564,7 +13415,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" ht="15">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -13584,7 +13435,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" ht="15">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -13604,7 +13455,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" ht="15">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -13624,7 +13475,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" ht="15">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -13644,7 +13495,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" ht="15">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -13664,7 +13515,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" ht="15">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -13684,7 +13535,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" ht="15">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -13704,7 +13555,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" ht="15">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -13724,7 +13575,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" ht="15">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -13744,7 +13595,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" ht="15">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -13764,7 +13615,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" ht="15">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -13784,7 +13635,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" ht="15">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -13804,341 +13655,257 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E196"/>
-      <c r="F196"/>
-    </row>
-    <row r="197" spans="1:18">
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E197"/>
-      <c r="F197"/>
-    </row>
-    <row r="198" spans="1:18">
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E198"/>
-      <c r="F198"/>
-    </row>
-    <row r="199" spans="1:18">
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E199"/>
-      <c r="F199"/>
-    </row>
-    <row r="200" spans="1:18">
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E200"/>
-      <c r="F200"/>
-    </row>
-    <row r="201" spans="1:18">
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E201"/>
-      <c r="F201"/>
-    </row>
-    <row r="202" spans="1:18">
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E202"/>
-      <c r="F202"/>
-    </row>
-    <row r="203" spans="1:18">
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E203"/>
-      <c r="F203"/>
-    </row>
-    <row r="204" spans="1:18">
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E204"/>
-      <c r="F204"/>
-    </row>
-    <row r="205" spans="1:18">
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E205"/>
-      <c r="F205"/>
-    </row>
-    <row r="206" spans="1:18">
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E206"/>
-      <c r="F206"/>
-    </row>
-    <row r="207" spans="1:18">
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E207"/>
-      <c r="F207"/>
-    </row>
-    <row r="208" spans="1:18">
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E208"/>
-      <c r="F208"/>
-    </row>
-    <row r="209" spans="5:6">
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E209"/>
-      <c r="F209"/>
-    </row>
-    <row r="210" spans="5:6">
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E210"/>
-      <c r="F210"/>
-    </row>
-    <row r="211" spans="5:6">
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E211"/>
-      <c r="F211"/>
-    </row>
-    <row r="212" spans="5:6">
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E212"/>
-      <c r="F212"/>
-    </row>
-    <row r="213" spans="5:6">
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E213"/>
-      <c r="F213"/>
-    </row>
-    <row r="214" spans="5:6">
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E214"/>
-      <c r="F214"/>
-    </row>
-    <row r="215" spans="5:6">
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E215"/>
-      <c r="F215"/>
-    </row>
-    <row r="216" spans="5:6">
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E216"/>
-      <c r="F216"/>
-    </row>
-    <row r="217" spans="5:6">
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E217"/>
-      <c r="F217"/>
-    </row>
-    <row r="218" spans="5:6">
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E218"/>
-      <c r="F218"/>
-    </row>
-    <row r="219" spans="5:6">
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E219"/>
-      <c r="F219"/>
-    </row>
-    <row r="220" spans="5:6">
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E220"/>
-      <c r="F220"/>
-    </row>
-    <row r="221" spans="5:6">
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E221"/>
-      <c r="F221"/>
-    </row>
-    <row r="222" spans="5:6">
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E222"/>
-      <c r="F222"/>
-    </row>
-    <row r="223" spans="5:6">
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E223"/>
-      <c r="F223"/>
-    </row>
-    <row r="224" spans="5:6">
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E224"/>
-      <c r="F224"/>
-    </row>
-    <row r="225" spans="5:6">
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E225"/>
-      <c r="F225"/>
-    </row>
-    <row r="226" spans="5:6">
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E226"/>
-      <c r="F226"/>
-    </row>
-    <row r="227" spans="5:6">
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E227"/>
-      <c r="F227"/>
-    </row>
-    <row r="228" spans="5:6">
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E228"/>
-      <c r="F228"/>
-    </row>
-    <row r="229" spans="5:6">
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E229"/>
-      <c r="F229"/>
-    </row>
-    <row r="230" spans="5:6">
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E230"/>
-      <c r="F230"/>
-    </row>
-    <row r="231" spans="5:6">
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E231"/>
-      <c r="F231"/>
-    </row>
-    <row r="232" spans="5:6">
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E232"/>
-      <c r="F232"/>
-    </row>
-    <row r="233" spans="5:6">
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E233"/>
-      <c r="F233"/>
-    </row>
-    <row r="234" spans="5:6">
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E234"/>
-      <c r="F234"/>
-    </row>
-    <row r="235" spans="5:6">
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E235"/>
-      <c r="F235"/>
-    </row>
-    <row r="236" spans="5:6">
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E236"/>
-      <c r="F236"/>
-    </row>
-    <row r="237" spans="5:6">
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E237"/>
-      <c r="F237"/>
-    </row>
-    <row r="238" spans="5:6">
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E238"/>
-      <c r="F238"/>
-    </row>
-    <row r="239" spans="5:6">
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E239"/>
-      <c r="F239"/>
-    </row>
-    <row r="240" spans="5:6">
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E240"/>
-      <c r="F240"/>
-    </row>
-    <row r="241" spans="5:6">
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E241"/>
-      <c r="F241"/>
-    </row>
-    <row r="242" spans="5:6">
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E242"/>
-      <c r="F242"/>
-    </row>
-    <row r="243" spans="5:6">
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E243"/>
-      <c r="F243"/>
-    </row>
-    <row r="244" spans="5:6">
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E244"/>
-      <c r="F244"/>
-    </row>
-    <row r="245" spans="5:6">
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E245"/>
-      <c r="F245"/>
-    </row>
-    <row r="246" spans="5:6">
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E246"/>
-      <c r="F246"/>
-    </row>
-    <row r="247" spans="5:6">
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E247"/>
-      <c r="F247"/>
-    </row>
-    <row r="248" spans="5:6">
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E248"/>
-      <c r="F248"/>
-    </row>
-    <row r="249" spans="5:6">
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E249"/>
-      <c r="F249"/>
-    </row>
-    <row r="250" spans="5:6">
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E250"/>
-      <c r="F250"/>
-    </row>
-    <row r="251" spans="5:6">
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E251"/>
-      <c r="F251"/>
-    </row>
-    <row r="252" spans="5:6">
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E252"/>
-      <c r="F252"/>
-    </row>
-    <row r="253" spans="5:6">
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E253"/>
-      <c r="F253"/>
-    </row>
-    <row r="254" spans="5:6">
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E254"/>
-      <c r="F254"/>
-    </row>
-    <row r="255" spans="5:6">
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E255"/>
-      <c r="F255"/>
-    </row>
-    <row r="256" spans="5:6">
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E256"/>
-      <c r="F256"/>
-    </row>
-    <row r="257" spans="5:6">
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E257"/>
-      <c r="F257"/>
-    </row>
-    <row r="258" spans="5:6">
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E258"/>
-      <c r="F258"/>
-    </row>
-    <row r="259" spans="5:6">
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E259"/>
-      <c r="F259"/>
-    </row>
-    <row r="260" spans="5:6">
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E260"/>
-      <c r="F260"/>
-    </row>
-    <row r="261" spans="5:6">
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E261"/>
-      <c r="F261"/>
-    </row>
-    <row r="262" spans="5:6">
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E262"/>
-      <c r="F262"/>
-    </row>
-    <row r="263" spans="5:6">
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E263"/>
-      <c r="F263"/>
-    </row>
-    <row r="264" spans="5:6">
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E264"/>
-      <c r="F264"/>
-    </row>
-    <row r="265" spans="5:6">
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E265"/>
-      <c r="F265"/>
-    </row>
-    <row r="266" spans="5:6">
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E266"/>
-      <c r="F266"/>
-    </row>
-    <row r="267" spans="5:6">
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E267"/>
-      <c r="F267"/>
-    </row>
-    <row r="268" spans="5:6">
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E268"/>
-      <c r="F268"/>
-    </row>
-    <row r="269" spans="5:6">
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E269"/>
-      <c r="F269"/>
-    </row>
-    <row r="270" spans="5:6">
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E270"/>
-      <c r="F270"/>
-    </row>
-    <row r="271" spans="5:6">
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E271"/>
-      <c r="F271"/>
-    </row>
-    <row r="272" spans="5:6">
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E272"/>
-      <c r="F272"/>
-    </row>
-    <row r="273" spans="5:6">
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E273"/>
-      <c r="F273"/>
-    </row>
-    <row r="274" spans="5:6">
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E274"/>
-      <c r="F274"/>
-    </row>
-    <row r="275" spans="5:6">
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E275"/>
-      <c r="F275"/>
-    </row>
-    <row r="276" spans="5:6">
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E276"/>
-      <c r="F276"/>
-    </row>
-    <row r="277" spans="5:6">
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E277"/>
-      <c r="F277"/>
-    </row>
-    <row r="278" spans="5:6">
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E278"/>
-      <c r="F278"/>
-    </row>
-    <row r="279" spans="5:6">
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E279"/>
-      <c r="F279"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -14157,7 +13924,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDFCCAD-07F9-4768-B22C-3C9115DDA520}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7469D2E-9B0D-4D16-8D1B-161AB8AC666C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F78C05B-451B-47CD-BEB3-6EBF584195C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1234,11 +1234,17 @@
       <c r="B19" s="30">
         <v>46091</v>
       </c>
-      <c r="C19" s="12"/>
+      <c r="C19" s="12">
+        <v>267570</v>
+      </c>
       <c r="D19" s="35"/>
-      <c r="E19" s="37"/>
+      <c r="E19" s="37">
+        <v>477.75</v>
+      </c>
       <c r="F19" s="37"/>
-      <c r="G19" s="11"/>
+      <c r="G19" s="12">
+        <v>50</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1812,7 +1818,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2126247</v>
+        <v>2393817</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -1820,7 +1826,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>928.5</v>
+        <v>1406.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1828,7 +1834,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -5144,7 +5150,7 @@
     <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5618,10 +5624,16 @@
       <c r="B19" s="30">
         <v>46091</v>
       </c>
-      <c r="C19" s="12"/>
+      <c r="C19" s="12">
+        <v>266386.58333333331</v>
+      </c>
       <c r="D19" s="35"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
+      <c r="E19" s="37">
+        <v>39.92</v>
+      </c>
+      <c r="F19" s="37">
+        <v>648</v>
+      </c>
       <c r="G19" s="11"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -6196,7 +6208,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1915439.5</v>
+        <v>2181826.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -6204,11 +6216,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>0</v>
+        <v>39.92</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>9810</v>
+        <v>10458</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10007,10 +10019,16 @@
       <c r="B19" s="30">
         <v>46091</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="35"/>
+      <c r="C19" s="12">
+        <v>281186</v>
+      </c>
+      <c r="D19" s="35">
+        <v>149.75</v>
+      </c>
       <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
+      <c r="F19" s="37">
+        <v>1128</v>
+      </c>
       <c r="G19" s="11"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -10585,11 +10603,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1890073</v>
+        <v>2171259</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>288.5</v>
+        <v>438.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10597,7 +10615,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>8274</v>
+        <v>9402</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F78C05B-451B-47CD-BEB3-6EBF584195C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0607F600-B5F7-4E0F-898E-57DBDD1DEAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -359,7 +359,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -431,6 +431,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1264,10 +1265,16 @@
       <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="35"/>
+      <c r="C20" s="36">
+        <v>320439</v>
+      </c>
+      <c r="D20" s="35">
+        <v>297</v>
+      </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
+      <c r="F20" s="43">
+        <v>1938</v>
+      </c>
       <c r="G20" s="35"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1818,11 +1825,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2393817</v>
+        <v>2714256</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>3250.5</v>
+        <v>3547.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1830,7 +1837,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>8514</v>
+        <v>10452</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5654,11 +5661,19 @@
       <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="35"/>
+      <c r="C20" s="36">
+        <v>268786</v>
+      </c>
+      <c r="D20" s="35">
+        <v>1173.5</v>
+      </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+      <c r="F20" s="43">
+        <v>1776</v>
+      </c>
+      <c r="G20" s="43">
+        <v>50</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -6208,11 +6223,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2181826.0833333335</v>
+        <v>2450612.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>4572.5</v>
+        <v>5746</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6220,11 +6235,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>10458</v>
+        <v>12234</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -10049,11 +10064,19 @@
       <c r="B20" s="30">
         <v>46092</v>
       </c>
-      <c r="C20" s="36"/>
+      <c r="C20" s="36">
+        <v>349583</v>
+      </c>
       <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+      <c r="E20" s="43">
+        <v>112</v>
+      </c>
+      <c r="F20" s="43">
+        <v>2388</v>
+      </c>
+      <c r="G20" s="43">
+        <v>50</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -10603,7 +10626,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2171259</v>
+        <v>2520842</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10611,15 +10634,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1848</v>
+        <v>1960</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>9402</v>
+        <v>11790</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0607F600-B5F7-4E0F-898E-57DBDD1DEAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C88114-9907-4FA8-AB52-AC980E31B08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -422,6 +422,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -431,7 +432,6 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -980,13 +980,13 @@
       <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1124,13 +1124,13 @@
       <c r="B15" s="30">
         <v>46087</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1178,13 +1178,13 @@
       <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1272,7 +1272,7 @@
         <v>297</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="43">
+      <c r="F20" s="40">
         <v>1938</v>
       </c>
       <c r="G20" s="35"/>
@@ -1295,10 +1295,16 @@
       <c r="B21" s="30">
         <v>46093</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="12">
+        <v>335528</v>
+      </c>
+      <c r="D21" s="13">
+        <v>178.5</v>
+      </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="39"/>
+      <c r="F21" s="39">
+        <v>2268</v>
+      </c>
       <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1367,13 +1373,13 @@
       <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -1537,13 +1543,13 @@
       <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -1707,13 +1713,13 @@
       <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -1825,11 +1831,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2714256</v>
+        <v>3049784</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>3547.5</v>
+        <v>3726</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1837,7 +1843,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>10452</v>
+        <v>12720</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5371,13 +5377,13 @@
       <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -5519,13 +5525,13 @@
       <c r="B15" s="30">
         <v>46087</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -5575,13 +5581,13 @@
       <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -5668,10 +5674,10 @@
         <v>1173.5</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="43">
+      <c r="F20" s="40">
         <v>1776</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="40">
         <v>50</v>
       </c>
       <c r="H20" s="1"/>
@@ -5693,10 +5699,16 @@
       <c r="B21" s="30">
         <v>46093</v>
       </c>
-      <c r="C21" s="12"/>
+      <c r="C21" s="12">
+        <v>383159</v>
+      </c>
       <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="39"/>
+      <c r="E21" s="12">
+        <v>580.5</v>
+      </c>
+      <c r="F21" s="39">
+        <v>2160</v>
+      </c>
       <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5765,13 +5777,13 @@
       <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -5935,13 +5947,13 @@
       <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -6105,13 +6117,13 @@
       <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -6223,7 +6235,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2450612.0833333335</v>
+        <v>2833771.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -6231,11 +6243,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>39.92</v>
+        <v>620.41999999999996</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>12234</v>
+        <v>14394</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -9769,13 +9781,13 @@
       <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -9889,13 +9901,13 @@
       <c r="B14" s="30">
         <v>46086</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -9978,13 +9990,13 @@
       <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -10068,13 +10080,13 @@
         <v>349583</v>
       </c>
       <c r="D20" s="35"/>
-      <c r="E20" s="43">
+      <c r="E20" s="40">
         <v>112</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="40">
         <v>2388</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="40">
         <v>50</v>
       </c>
       <c r="H20" s="1"/>
@@ -10096,10 +10108,16 @@
       <c r="B21" s="30">
         <v>46093</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="12">
+        <v>320630</v>
+      </c>
+      <c r="D21" s="13">
+        <v>437.25</v>
+      </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="39"/>
+      <c r="F21" s="39">
+        <v>1890</v>
+      </c>
       <c r="G21" s="34"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -10168,13 +10186,13 @@
       <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -10338,13 +10356,13 @@
       <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -10508,13 +10526,13 @@
       <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -10626,11 +10644,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2520842</v>
+        <v>2841472</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>438.25</v>
+        <v>875.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10638,7 +10656,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>11790</v>
+        <v>13680</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C88114-9907-4FA8-AB52-AC980E31B08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A310A2F1-830A-4EA7-8D0D-88880BC2A600}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -31,12 +31,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="19">
   <si>
     <t>SALES</t>
   </si>
@@ -147,10 +142,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,8 +351,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -369,23 +364,23 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -403,33 +398,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -773,23 +768,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.25" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="16.5">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -811,7 +806,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -831,7 +826,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>16</v>
@@ -853,7 +848,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -875,7 +870,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>7</v>
@@ -897,7 +892,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>11</v>
@@ -919,7 +914,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -939,7 +934,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
@@ -973,7 +968,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -999,7 +994,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -1029,7 +1024,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15">
       <c r="A12" s="11">
         <v>3</v>
       </c>
@@ -1057,7 +1052,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15">
       <c r="A13" s="11">
         <v>4</v>
       </c>
@@ -1087,7 +1082,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="15">
       <c r="A14" s="11">
         <v>5</v>
       </c>
@@ -1117,7 +1112,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="15">
       <c r="A15" s="11">
         <v>6</v>
       </c>
@@ -1143,7 +1138,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="15">
       <c r="A16" s="11">
         <v>7</v>
       </c>
@@ -1171,7 +1166,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" s="11">
         <v>8</v>
       </c>
@@ -1197,7 +1192,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="15">
       <c r="A18" s="11">
         <v>9</v>
       </c>
@@ -1228,7 +1223,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="15">
       <c r="A19" s="11">
         <v>10</v>
       </c>
@@ -1258,7 +1253,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15">
       <c r="A20" s="11">
         <v>11</v>
       </c>
@@ -1288,7 +1283,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="15">
       <c r="A21" s="11">
         <v>12</v>
       </c>
@@ -1318,18 +1313,20 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="15">
       <c r="A22" s="11">
         <v>13</v>
       </c>
       <c r="B22" s="30">
         <v>46094</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1342,7 +1339,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15">
       <c r="A23" s="11">
         <v>14</v>
       </c>
@@ -1366,7 +1363,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="15">
       <c r="A24" s="11">
         <v>15</v>
       </c>
@@ -1392,7 +1389,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="15">
       <c r="A25" s="11">
         <v>16</v>
       </c>
@@ -1416,7 +1413,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15">
       <c r="A26" s="11">
         <v>17</v>
       </c>
@@ -1440,7 +1437,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" s="11">
         <v>18</v>
       </c>
@@ -1464,7 +1461,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="15">
       <c r="A28" s="11">
         <v>19</v>
       </c>
@@ -1488,7 +1485,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="15">
       <c r="A29" s="11">
         <v>20</v>
       </c>
@@ -1512,7 +1509,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15">
       <c r="A30" s="11">
         <v>21</v>
       </c>
@@ -1536,7 +1533,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15">
       <c r="A31" s="11">
         <v>22</v>
       </c>
@@ -1562,7 +1559,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15">
       <c r="A32" s="11">
         <v>23</v>
       </c>
@@ -1586,7 +1583,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="15">
       <c r="A33" s="11">
         <v>24</v>
       </c>
@@ -1610,7 +1607,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="15">
       <c r="A34" s="11">
         <v>25</v>
       </c>
@@ -1634,7 +1631,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="15">
       <c r="A35" s="11">
         <v>26</v>
       </c>
@@ -1658,7 +1655,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="15">
       <c r="A36" s="11">
         <v>27</v>
       </c>
@@ -1682,7 +1679,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="15">
       <c r="A37" s="11">
         <v>28</v>
       </c>
@@ -1706,7 +1703,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="15">
       <c r="A38" s="11">
         <v>29</v>
       </c>
@@ -1732,7 +1729,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="15">
       <c r="A39" s="11">
         <v>30</v>
       </c>
@@ -1756,7 +1753,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="15">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -1780,7 +1777,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="15">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -1802,7 +1799,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="15">
       <c r="A42" s="23">
         <v>31</v>
       </c>
@@ -1824,7 +1821,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="15">
       <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
@@ -1861,7 +1858,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="15">
       <c r="A44" s="1"/>
       <c r="B44" s="32"/>
       <c r="C44" s="22"/>
@@ -1881,7 +1878,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="15">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1901,7 +1898,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="15">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1921,7 +1918,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="15">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1941,7 +1938,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="15">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1961,7 +1958,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="15">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1981,7 +1978,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2001,7 +1998,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="15">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2021,7 +2018,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="15">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2041,7 +2038,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="15">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2061,7 +2058,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="15">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2081,7 +2078,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="15">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2101,7 +2098,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2121,7 +2118,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="15">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2141,7 +2138,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2161,7 +2158,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="15">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2181,7 +2178,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="15">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2201,7 +2198,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="15">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2221,7 +2218,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="15">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2241,7 +2238,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2261,7 +2258,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="15">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2281,7 +2278,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="15">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2301,7 +2298,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2321,7 +2318,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="15">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2341,7 +2338,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="15">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2361,7 +2358,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="15">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2381,7 +2378,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="15">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2401,7 +2398,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2421,7 +2418,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="15">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2441,7 +2438,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="15">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2461,7 +2458,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2481,7 +2478,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2501,7 +2498,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2521,7 +2518,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2541,7 +2538,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2561,7 +2558,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2581,7 +2578,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2601,7 +2598,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="15">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2621,7 +2618,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="15">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2641,7 +2638,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="15">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2661,7 +2658,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2681,7 +2678,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2701,7 +2698,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2721,7 +2718,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2741,7 +2738,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2761,7 +2758,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2781,7 +2778,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2801,7 +2798,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2821,7 +2818,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2841,7 +2838,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2861,7 +2858,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2881,7 +2878,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -2901,7 +2898,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -2921,7 +2918,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -2941,7 +2938,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -2961,7 +2958,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -2981,7 +2978,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3001,7 +2998,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3021,7 +3018,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3041,7 +3038,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3061,7 +3058,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3081,7 +3078,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3101,7 +3098,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="15">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3121,7 +3118,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="15">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3141,7 +3138,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="15">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3161,7 +3158,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="15">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3181,7 +3178,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3201,7 +3198,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="15">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3221,7 +3218,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="15">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3241,7 +3238,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="15">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3261,7 +3258,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="15">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3281,7 +3278,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="15">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3301,7 +3298,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="15">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3321,7 +3318,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="15">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3341,7 +3338,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="15">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3361,7 +3358,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="15">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3381,7 +3378,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="15">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3401,7 +3398,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="15">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3421,7 +3418,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="15">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3441,7 +3438,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="15">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3461,7 +3458,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="15">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3481,7 +3478,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="15">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3501,7 +3498,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="15">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3521,7 +3518,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="15">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3541,7 +3538,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="15">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3561,7 +3558,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="15">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3581,7 +3578,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="15">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -3601,7 +3598,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="15">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -3621,7 +3618,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="15">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -3641,7 +3638,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="15">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -3661,7 +3658,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="15">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -3681,7 +3678,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="15">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -3701,7 +3698,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="15">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -3721,7 +3718,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="15">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -3741,7 +3738,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="15">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -3761,7 +3758,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="15">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -3781,7 +3778,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="15">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -3801,7 +3798,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="15">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -3821,7 +3818,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="15">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -3841,7 +3838,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="15">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -3861,7 +3858,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="15">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -3881,7 +3878,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="15">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -3901,7 +3898,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="15">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -3921,7 +3918,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -3941,7 +3938,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="15">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -3961,7 +3958,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="15">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -3981,7 +3978,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="15">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4001,7 +3998,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="15">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4021,7 +4018,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="15">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4041,7 +4038,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="15">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4061,7 +4058,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="15">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4081,7 +4078,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="15">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4101,7 +4098,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="15">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4121,7 +4118,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="15">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4141,7 +4138,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="15">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4161,7 +4158,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="15">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4181,7 +4178,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="15">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4201,7 +4198,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="15">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4221,7 +4218,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="15">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4241,7 +4238,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="15">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4261,7 +4258,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="15">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4281,7 +4278,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="15">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4301,7 +4298,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="15">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4321,7 +4318,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="15">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4341,7 +4338,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="15">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4361,7 +4358,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="15">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4381,7 +4378,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="15">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4401,7 +4398,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="15">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4421,7 +4418,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="15">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4441,7 +4438,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="15">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4461,7 +4458,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="15">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4481,7 +4478,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="15">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4501,7 +4498,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="15">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4521,7 +4518,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="15">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4541,7 +4538,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="15">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4561,7 +4558,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="15">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4581,7 +4578,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="15">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -4601,7 +4598,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="15">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -4621,7 +4618,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="15">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -4641,7 +4638,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="15">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -4661,7 +4658,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="15">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -4681,7 +4678,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="15">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -4701,7 +4698,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="15">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -4721,7 +4718,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="15">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -4741,7 +4738,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="15">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -4761,7 +4758,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="15">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -4781,7 +4778,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="15">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -4801,7 +4798,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="15">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -4821,7 +4818,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="15">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -4841,7 +4838,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="15">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -4861,7 +4858,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="15">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -4881,7 +4878,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="15">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -4901,266 +4898,267 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18">
       <c r="E196"/>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18">
       <c r="E197"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18">
       <c r="E198"/>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18">
       <c r="E199"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18">
       <c r="E200"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18">
       <c r="E201"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18">
       <c r="E202"/>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18">
       <c r="E203"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18">
       <c r="E204"/>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18">
       <c r="E205"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18">
       <c r="E206"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18">
       <c r="E207"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18">
       <c r="E208"/>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="5:5">
       <c r="E209"/>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="5:5">
       <c r="E210"/>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="5:5">
       <c r="E211"/>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="5:5">
       <c r="E212"/>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="5:5">
       <c r="E213"/>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="5:5">
       <c r="E214"/>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="5:5">
       <c r="E215"/>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="5:5">
       <c r="E216"/>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="5:5">
       <c r="E217"/>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="5:5">
       <c r="E218"/>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="5:5">
       <c r="E219"/>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="5:5">
       <c r="E220"/>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="5:5">
       <c r="E221"/>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="5:5">
       <c r="E222"/>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="5:5">
       <c r="E223"/>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="5:5">
       <c r="E224"/>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="5:5">
       <c r="E225"/>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="5:5">
       <c r="E226"/>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="5:5">
       <c r="E227"/>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="5:5">
       <c r="E228"/>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="5:5">
       <c r="E229"/>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="5:5">
       <c r="E230"/>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="5:5">
       <c r="E231"/>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="5:5">
       <c r="E232"/>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="5:5">
       <c r="E233"/>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="5:5">
       <c r="E234"/>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="5:5">
       <c r="E235"/>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="5:5">
       <c r="E236"/>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="5:5">
       <c r="E237"/>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="5:5">
       <c r="E238"/>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="5:5">
       <c r="E239"/>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="5:5">
       <c r="E240"/>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="5:5">
       <c r="E241"/>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="5:5">
       <c r="E242"/>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="5:5">
       <c r="E243"/>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="5:5">
       <c r="E244"/>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="5:5">
       <c r="E245"/>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="5:5">
       <c r="E246"/>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="5:5">
       <c r="E247"/>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="5:5">
       <c r="E248"/>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="5:5">
       <c r="E249"/>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="5:5">
       <c r="E250"/>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="5:5">
       <c r="E251"/>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="5:5">
       <c r="E252"/>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="5:5">
       <c r="E253"/>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="5:5">
       <c r="E254"/>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="5:5">
       <c r="E255"/>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="5:5">
       <c r="E256"/>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="5:5">
       <c r="E257"/>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="5:5">
       <c r="E258"/>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="5:5">
       <c r="E259"/>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="5:5">
       <c r="E260"/>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="5:5">
       <c r="E261"/>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="5:5">
       <c r="E262"/>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="5:5">
       <c r="E263"/>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="5:5">
       <c r="E264"/>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="5:5">
       <c r="E265"/>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="5:5">
       <c r="E266"/>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="5:5">
       <c r="E267"/>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="5:5">
       <c r="E268"/>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="5:5">
       <c r="E269"/>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="5:5">
       <c r="E270"/>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="5:5">
       <c r="E271"/>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="5:5">
       <c r="E272"/>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="5:5">
       <c r="E273"/>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="5:5">
       <c r="E274"/>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="5:5">
       <c r="E275"/>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="5:5">
       <c r="E276"/>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="5:5">
       <c r="E277"/>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="5:5">
       <c r="E278"/>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="5:5">
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5170,23 +5168,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E574FF03-14F0-421D-8F76-5519CF1A2460}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.25" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="16.5">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -5208,7 +5206,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5228,7 +5226,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>15</v>
@@ -5250,7 +5248,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -5272,7 +5270,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -5294,7 +5292,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>14</v>
@@ -5316,7 +5314,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -5336,7 +5334,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
@@ -5370,7 +5368,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -5396,7 +5394,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -5426,7 +5424,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15">
       <c r="A12" s="11">
         <v>3</v>
       </c>
@@ -5456,7 +5454,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15">
       <c r="A13" s="11">
         <v>4</v>
       </c>
@@ -5488,7 +5486,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="15">
       <c r="A14" s="11">
         <v>5</v>
       </c>
@@ -5518,7 +5516,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="15">
       <c r="A15" s="11">
         <v>6</v>
       </c>
@@ -5544,7 +5542,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="15">
       <c r="A16" s="11">
         <v>7</v>
       </c>
@@ -5574,7 +5572,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" s="11">
         <v>8</v>
       </c>
@@ -5600,7 +5598,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="15">
       <c r="A18" s="11">
         <v>9</v>
       </c>
@@ -5630,7 +5628,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="15">
       <c r="A19" s="11">
         <v>10</v>
       </c>
@@ -5660,7 +5658,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15">
       <c r="A20" s="11">
         <v>11</v>
       </c>
@@ -5692,7 +5690,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="15">
       <c r="A21" s="11">
         <v>12</v>
       </c>
@@ -5722,18 +5720,20 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="15">
       <c r="A22" s="11">
         <v>13</v>
       </c>
       <c r="B22" s="30">
         <v>46094</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5746,7 +5746,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15">
       <c r="A23" s="11">
         <v>14</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="15">
       <c r="A24" s="11">
         <v>15</v>
       </c>
@@ -5796,7 +5796,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="15">
       <c r="A25" s="11">
         <v>16</v>
       </c>
@@ -5820,7 +5820,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15">
       <c r="A26" s="11">
         <v>17</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" s="11">
         <v>18</v>
       </c>
@@ -5868,7 +5868,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="15">
       <c r="A28" s="11">
         <v>19</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="15">
       <c r="A29" s="11">
         <v>20</v>
       </c>
@@ -5916,7 +5916,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15">
       <c r="A30" s="11">
         <v>21</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15">
       <c r="A31" s="11">
         <v>22</v>
       </c>
@@ -5966,7 +5966,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15">
       <c r="A32" s="11">
         <v>23</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="15">
       <c r="A33" s="11">
         <v>24</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="15">
       <c r="A34" s="11">
         <v>25</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="15">
       <c r="A35" s="11">
         <v>26</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="15">
       <c r="A36" s="11">
         <v>27</v>
       </c>
@@ -6086,7 +6086,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="15">
       <c r="A37" s="11">
         <v>28</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="15">
       <c r="A38" s="11">
         <v>29</v>
       </c>
@@ -6136,7 +6136,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="15">
       <c r="A39" s="11">
         <v>30</v>
       </c>
@@ -6160,7 +6160,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="15">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="15">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="15">
       <c r="A42" s="23">
         <v>31</v>
       </c>
@@ -6228,7 +6228,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="15">
       <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
@@ -6265,7 +6265,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="15">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
@@ -6285,7 +6285,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="15">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -6305,7 +6305,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="15">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -6325,7 +6325,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="15">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -6345,7 +6345,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="15">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -6365,7 +6365,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="15">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -6385,7 +6385,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -6405,7 +6405,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="15">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -6425,7 +6425,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="15">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -6445,7 +6445,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="15">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -6465,7 +6465,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="15">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -6485,7 +6485,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="15">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -6505,7 +6505,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -6525,7 +6525,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="15">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -6545,7 +6545,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -6565,7 +6565,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="15">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -6585,7 +6585,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="15">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -6605,7 +6605,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="15">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -6625,7 +6625,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="15">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -6645,7 +6645,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6665,7 +6665,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="15">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6685,7 +6685,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="15">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -6705,7 +6705,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -6725,7 +6725,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="15">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -6745,7 +6745,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="15">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6765,7 +6765,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="15">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6785,7 +6785,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="15">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6805,7 +6805,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -6825,7 +6825,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="15">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -6845,7 +6845,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="15">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -6865,7 +6865,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6885,7 +6885,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6905,7 +6905,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6925,7 +6925,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6945,7 +6945,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6965,7 +6965,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6985,7 +6985,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -7005,7 +7005,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="15">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7025,7 +7025,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="15">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7045,7 +7045,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="15">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7065,7 +7065,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7085,7 +7085,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7105,7 +7105,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7125,7 +7125,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7145,7 +7145,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7165,7 +7165,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7185,7 +7185,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7205,7 +7205,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7225,7 +7225,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7245,7 +7245,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7265,7 +7265,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7285,7 +7285,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7305,7 +7305,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7325,7 +7325,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7345,7 +7345,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7365,7 +7365,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7385,7 +7385,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7405,7 +7405,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7425,7 +7425,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7445,7 +7445,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7465,7 +7465,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7485,7 +7485,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7505,7 +7505,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="15">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7525,7 +7525,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="15">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7545,7 +7545,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="15">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7565,7 +7565,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="15">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7585,7 +7585,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7605,7 +7605,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="15">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7625,7 +7625,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="15">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7645,7 +7645,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="15">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7665,7 +7665,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="15">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7685,7 +7685,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="15">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7705,7 +7705,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="15">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7725,7 +7725,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="15">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7745,7 +7745,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="15">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7765,7 +7765,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="15">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7785,7 +7785,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="15">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7805,7 +7805,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="15">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7825,7 +7825,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="15">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7845,7 +7845,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="15">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7865,7 +7865,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="15">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7885,7 +7885,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="15">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -7905,7 +7905,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="15">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7925,7 +7925,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="15">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7945,7 +7945,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="15">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7965,7 +7965,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="15">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -7985,7 +7985,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="15">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8005,7 +8005,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="15">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -8025,7 +8025,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="15">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -8045,7 +8045,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="15">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -8065,7 +8065,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="15">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -8085,7 +8085,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="15">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -8105,7 +8105,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="15">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -8125,7 +8125,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="15">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -8145,7 +8145,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="15">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -8165,7 +8165,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="15">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8185,7 +8185,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="15">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -8205,7 +8205,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="15">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -8225,7 +8225,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="15">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -8245,7 +8245,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="15">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -8265,7 +8265,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="15">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -8285,7 +8285,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="15">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -8305,7 +8305,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="15">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -8325,7 +8325,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -8345,7 +8345,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="15">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -8365,7 +8365,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="15">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -8385,7 +8385,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="15">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -8405,7 +8405,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="15">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -8425,7 +8425,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="15">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -8445,7 +8445,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="15">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -8465,7 +8465,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="15">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -8485,7 +8485,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="15">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -8505,7 +8505,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="15">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -8525,7 +8525,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="15">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -8545,7 +8545,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="15">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -8565,7 +8565,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="15">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -8585,7 +8585,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="15">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -8605,7 +8605,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="15">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -8625,7 +8625,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="15">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8645,7 +8645,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="15">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8665,7 +8665,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="15">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -8685,7 +8685,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="15">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -8705,7 +8705,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="15">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -8725,7 +8725,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="15">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -8745,7 +8745,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="15">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8765,7 +8765,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="15">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8785,7 +8785,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="15">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8805,7 +8805,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="15">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8825,7 +8825,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="15">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8845,7 +8845,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="15">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8865,7 +8865,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="15">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8885,7 +8885,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="15">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8905,7 +8905,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="15">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8925,7 +8925,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="15">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8945,7 +8945,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="15">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8965,7 +8965,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="15">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8985,7 +8985,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="15">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -9005,7 +9005,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="15">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -9025,7 +9025,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="15">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -9045,7 +9045,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="15">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -9065,7 +9065,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="15">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -9085,7 +9085,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="15">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -9105,7 +9105,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="15">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -9125,7 +9125,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="15">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -9145,7 +9145,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="15">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -9165,7 +9165,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="15">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -9185,7 +9185,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="15">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -9205,7 +9205,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="15">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -9225,7 +9225,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="15">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -9245,7 +9245,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="15">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9265,7 +9265,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="15">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9285,7 +9285,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="15">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9305,266 +9305,267 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18">
       <c r="E196"/>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18">
       <c r="E197"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18">
       <c r="E198"/>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18">
       <c r="E199"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18">
       <c r="E200"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18">
       <c r="E201"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18">
       <c r="E202"/>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18">
       <c r="E203"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18">
       <c r="E204"/>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18">
       <c r="E205"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18">
       <c r="E206"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18">
       <c r="E207"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18">
       <c r="E208"/>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="5:5">
       <c r="E209"/>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="5:5">
       <c r="E210"/>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="5:5">
       <c r="E211"/>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="5:5">
       <c r="E212"/>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="5:5">
       <c r="E213"/>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="5:5">
       <c r="E214"/>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="5:5">
       <c r="E215"/>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="5:5">
       <c r="E216"/>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="5:5">
       <c r="E217"/>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="5:5">
       <c r="E218"/>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="5:5">
       <c r="E219"/>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="5:5">
       <c r="E220"/>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="5:5">
       <c r="E221"/>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="5:5">
       <c r="E222"/>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="5:5">
       <c r="E223"/>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="5:5">
       <c r="E224"/>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="5:5">
       <c r="E225"/>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="5:5">
       <c r="E226"/>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="5:5">
       <c r="E227"/>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="5:5">
       <c r="E228"/>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="5:5">
       <c r="E229"/>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="5:5">
       <c r="E230"/>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="5:5">
       <c r="E231"/>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="5:5">
       <c r="E232"/>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="5:5">
       <c r="E233"/>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="5:5">
       <c r="E234"/>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="5:5">
       <c r="E235"/>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="5:5">
       <c r="E236"/>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="5:5">
       <c r="E237"/>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="5:5">
       <c r="E238"/>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="5:5">
       <c r="E239"/>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="5:5">
       <c r="E240"/>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="5:5">
       <c r="E241"/>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="5:5">
       <c r="E242"/>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="5:5">
       <c r="E243"/>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="5:5">
       <c r="E244"/>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="5:5">
       <c r="E245"/>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="5:5">
       <c r="E246"/>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="5:5">
       <c r="E247"/>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="5:5">
       <c r="E248"/>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="5:5">
       <c r="E249"/>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="5:5">
       <c r="E250"/>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="5:5">
       <c r="E251"/>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="5:5">
       <c r="E252"/>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="5:5">
       <c r="E253"/>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="5:5">
       <c r="E254"/>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="5:5">
       <c r="E255"/>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="5:5">
       <c r="E256"/>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="5:5">
       <c r="E257"/>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="5:5">
       <c r="E258"/>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="5:5">
       <c r="E259"/>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="5:5">
       <c r="E260"/>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="5:5">
       <c r="E261"/>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="5:5">
       <c r="E262"/>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="5:5">
       <c r="E263"/>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="5:5">
       <c r="E264"/>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="5:5">
       <c r="E265"/>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="5:5">
       <c r="E266"/>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="5:5">
       <c r="E267"/>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="5:5">
       <c r="E268"/>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="5:5">
       <c r="E269"/>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="5:5">
       <c r="E270"/>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="5:5">
       <c r="E271"/>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="5:5">
       <c r="E272"/>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="5:5">
       <c r="E273"/>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="5:5">
       <c r="E274"/>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="5:5">
       <c r="E275"/>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="5:5">
       <c r="E276"/>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="5:5">
       <c r="E277"/>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="5:5">
       <c r="E278"/>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="5:5">
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9574,23 +9575,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
   <dimension ref="A1:R279"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.25" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="15" style="17" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="16.5">
       <c r="A2" s="2"/>
       <c r="B2" s="21" t="s">
         <v>8</v>
@@ -9612,7 +9613,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -9632,7 +9633,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>15</v>
@@ -9654,7 +9655,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15">
       <c r="A5" s="5"/>
       <c r="B5" s="20">
         <v>2026</v>
@@ -9676,7 +9677,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>10</v>
@@ -9698,7 +9699,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>13</v>
@@ -9720,7 +9721,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -9740,7 +9741,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
@@ -9774,7 +9775,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -9800,7 +9801,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -9832,7 +9833,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15">
       <c r="A12" s="11">
         <v>3</v>
       </c>
@@ -9862,7 +9863,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15">
       <c r="A13" s="11">
         <v>4</v>
       </c>
@@ -9894,7 +9895,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="15">
       <c r="A14" s="11">
         <v>5</v>
       </c>
@@ -9920,7 +9921,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="15">
       <c r="A15" s="11">
         <v>6</v>
       </c>
@@ -9953,7 +9954,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="15">
       <c r="A16" s="11">
         <v>7</v>
       </c>
@@ -9983,7 +9984,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" s="11">
         <v>8</v>
       </c>
@@ -10009,7 +10010,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="15">
       <c r="A18" s="11">
         <v>9</v>
       </c>
@@ -10039,7 +10040,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="15">
       <c r="A19" s="11">
         <v>10</v>
       </c>
@@ -10069,7 +10070,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15">
       <c r="A20" s="11">
         <v>11</v>
       </c>
@@ -10101,7 +10102,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="15">
       <c r="A21" s="11">
         <v>12</v>
       </c>
@@ -10131,18 +10132,20 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="15">
       <c r="A22" s="11">
         <v>13</v>
       </c>
       <c r="B22" s="30">
         <v>46094</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -10155,7 +10158,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15">
       <c r="A23" s="11">
         <v>14</v>
       </c>
@@ -10179,7 +10182,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="15">
       <c r="A24" s="11">
         <v>15</v>
       </c>
@@ -10205,7 +10208,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="15">
       <c r="A25" s="11">
         <v>16</v>
       </c>
@@ -10229,7 +10232,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15">
       <c r="A26" s="11">
         <v>17</v>
       </c>
@@ -10253,7 +10256,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" s="11">
         <v>18</v>
       </c>
@@ -10277,7 +10280,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="15">
       <c r="A28" s="11">
         <v>19</v>
       </c>
@@ -10301,7 +10304,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="15">
       <c r="A29" s="11">
         <v>20</v>
       </c>
@@ -10325,7 +10328,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15">
       <c r="A30" s="11">
         <v>21</v>
       </c>
@@ -10349,7 +10352,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15">
       <c r="A31" s="11">
         <v>22</v>
       </c>
@@ -10375,7 +10378,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15">
       <c r="A32" s="11">
         <v>23</v>
       </c>
@@ -10399,7 +10402,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="15">
       <c r="A33" s="11">
         <v>24</v>
       </c>
@@ -10423,7 +10426,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="15">
       <c r="A34" s="11">
         <v>25</v>
       </c>
@@ -10447,7 +10450,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="15">
       <c r="A35" s="11">
         <v>26</v>
       </c>
@@ -10471,7 +10474,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="15">
       <c r="A36" s="11">
         <v>27</v>
       </c>
@@ -10495,7 +10498,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="15">
       <c r="A37" s="11">
         <v>28</v>
       </c>
@@ -10519,7 +10522,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="15">
       <c r="A38" s="11">
         <v>29</v>
       </c>
@@ -10545,7 +10548,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="15">
       <c r="A39" s="11">
         <v>30</v>
       </c>
@@ -10569,7 +10572,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="15">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -10593,7 +10596,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="15">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -10615,7 +10618,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="15">
       <c r="A42" s="23">
         <v>31</v>
       </c>
@@ -10637,7 +10640,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="15">
       <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
@@ -10674,7 +10677,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="15">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
@@ -10694,7 +10697,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="15">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -10714,7 +10717,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="15">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -10734,7 +10737,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="15">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -10754,7 +10757,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="15">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -10774,7 +10777,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="15">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -10794,7 +10797,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -10814,7 +10817,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="15">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -10834,7 +10837,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="15">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -10854,7 +10857,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="15">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -10874,7 +10877,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="15">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -10894,7 +10897,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="15">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -10914,7 +10917,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -10934,7 +10937,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="15">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -10954,7 +10957,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -10974,7 +10977,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="15">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -10994,7 +10997,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="15">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -11014,7 +11017,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="15">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -11034,7 +11037,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="15">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -11054,7 +11057,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -11074,7 +11077,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="15">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -11094,7 +11097,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="15">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -11114,7 +11117,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -11134,7 +11137,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="15">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -11154,7 +11157,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="15">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -11174,7 +11177,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="15">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -11194,7 +11197,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="15">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -11214,7 +11217,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -11234,7 +11237,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="15">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -11254,7 +11257,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="15">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -11274,7 +11277,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -11294,7 +11297,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -11314,7 +11317,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -11334,7 +11337,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -11354,7 +11357,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -11374,7 +11377,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -11394,7 +11397,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -11414,7 +11417,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="15">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -11434,7 +11437,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="15">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -11454,7 +11457,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="15">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -11474,7 +11477,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -11494,7 +11497,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -11514,7 +11517,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -11534,7 +11537,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -11554,7 +11557,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -11574,7 +11577,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -11594,7 +11597,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -11614,7 +11617,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -11634,7 +11637,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -11654,7 +11657,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -11674,7 +11677,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -11694,7 +11697,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -11714,7 +11717,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -11734,7 +11737,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -11754,7 +11757,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -11774,7 +11777,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -11794,7 +11797,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -11814,7 +11817,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -11834,7 +11837,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -11854,7 +11857,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -11874,7 +11877,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -11894,7 +11897,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -11914,7 +11917,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="15">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -11934,7 +11937,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="15">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -11954,7 +11957,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="15">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -11974,7 +11977,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="15">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -11994,7 +11997,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -12014,7 +12017,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="15">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -12034,7 +12037,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="15">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -12054,7 +12057,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="15">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -12074,7 +12077,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="15">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -12094,7 +12097,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="15">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -12114,7 +12117,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="15">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -12134,7 +12137,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="15">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -12154,7 +12157,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="15">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -12174,7 +12177,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="15">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -12194,7 +12197,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="15">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12214,7 +12217,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="15">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12234,7 +12237,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="15">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12254,7 +12257,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="15">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12274,7 +12277,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="15">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12294,7 +12297,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="15">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -12314,7 +12317,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="15">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -12334,7 +12337,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="15">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -12354,7 +12357,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="15">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -12374,7 +12377,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="15">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -12394,7 +12397,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="15">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -12414,7 +12417,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="15">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -12434,7 +12437,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="15">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -12454,7 +12457,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="15">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -12474,7 +12477,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="15">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -12494,7 +12497,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="15">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -12514,7 +12517,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="15">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -12534,7 +12537,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="15">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -12554,7 +12557,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="15">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -12574,7 +12577,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="15">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -12594,7 +12597,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="15">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -12614,7 +12617,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="15">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -12634,7 +12637,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="15">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -12654,7 +12657,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="15">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -12674,7 +12677,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="15">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -12694,7 +12697,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="15">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -12714,7 +12717,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="15">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -12734,7 +12737,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -12754,7 +12757,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="15">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -12774,7 +12777,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="15">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -12794,7 +12797,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="15">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -12814,7 +12817,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="15">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -12834,7 +12837,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="15">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -12854,7 +12857,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="15">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -12874,7 +12877,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="15">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -12894,7 +12897,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="15">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -12914,7 +12917,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="15">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -12934,7 +12937,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="15">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -12954,7 +12957,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="15">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -12974,7 +12977,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="15">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -12994,7 +12997,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="15">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -13014,7 +13017,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="15">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -13034,7 +13037,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="15">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -13054,7 +13057,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="15">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -13074,7 +13077,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="15">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -13094,7 +13097,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="15">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -13114,7 +13117,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="15">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -13134,7 +13137,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="15">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -13154,7 +13157,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="15">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -13174,7 +13177,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="15">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -13194,7 +13197,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="15">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -13214,7 +13217,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="15">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -13234,7 +13237,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="15">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -13254,7 +13257,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="15">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -13274,7 +13277,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="15">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -13294,7 +13297,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="15">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -13314,7 +13317,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="15">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -13334,7 +13337,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="15">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -13354,7 +13357,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="15">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -13374,7 +13377,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="15">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -13394,7 +13397,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="15">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -13414,7 +13417,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="15">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -13434,7 +13437,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="15">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -13454,7 +13457,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="15">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -13474,7 +13477,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="15">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -13494,7 +13497,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="15">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -13514,7 +13517,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="15">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -13534,7 +13537,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="15">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -13554,7 +13557,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="15">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -13574,7 +13577,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="15">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -13594,7 +13597,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="15">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -13614,7 +13617,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="15">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -13634,7 +13637,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="15">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -13654,7 +13657,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="15">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -13674,7 +13677,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="15">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -13694,7 +13697,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="15">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -13714,266 +13717,267 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18">
       <c r="E196"/>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18">
       <c r="E197"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18">
       <c r="E198"/>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18">
       <c r="E199"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18">
       <c r="E200"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18">
       <c r="E201"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18">
       <c r="E202"/>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18">
       <c r="E203"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18">
       <c r="E204"/>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18">
       <c r="E205"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18">
       <c r="E206"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18">
       <c r="E207"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18">
       <c r="E208"/>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="5:5">
       <c r="E209"/>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="5:5">
       <c r="E210"/>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="5:5">
       <c r="E211"/>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="5:5">
       <c r="E212"/>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="5:5">
       <c r="E213"/>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="5:5">
       <c r="E214"/>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="5:5">
       <c r="E215"/>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="5:5">
       <c r="E216"/>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="5:5">
       <c r="E217"/>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="5:5">
       <c r="E218"/>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="5:5">
       <c r="E219"/>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="5:5">
       <c r="E220"/>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="5:5">
       <c r="E221"/>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="5:5">
       <c r="E222"/>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="5:5">
       <c r="E223"/>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="5:5">
       <c r="E224"/>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="5:5">
       <c r="E225"/>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="5:5">
       <c r="E226"/>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="5:5">
       <c r="E227"/>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="5:5">
       <c r="E228"/>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="5:5">
       <c r="E229"/>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="5:5">
       <c r="E230"/>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="5:5">
       <c r="E231"/>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="5:5">
       <c r="E232"/>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="5:5">
       <c r="E233"/>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="5:5">
       <c r="E234"/>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="5:5">
       <c r="E235"/>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="5:5">
       <c r="E236"/>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="5:5">
       <c r="E237"/>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="5:5">
       <c r="E238"/>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="5:5">
       <c r="E239"/>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="5:5">
       <c r="E240"/>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="5:5">
       <c r="E241"/>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="5:5">
       <c r="E242"/>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="5:5">
       <c r="E243"/>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="5:5">
       <c r="E244"/>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="5:5">
       <c r="E245"/>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="5:5">
       <c r="E246"/>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="5:5">
       <c r="E247"/>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="5:5">
       <c r="E248"/>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="5:5">
       <c r="E249"/>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="5:5">
       <c r="E250"/>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="5:5">
       <c r="E251"/>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="5:5">
       <c r="E252"/>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="5:5">
       <c r="E253"/>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="5:5">
       <c r="E254"/>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="5:5">
       <c r="E255"/>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="5:5">
       <c r="E256"/>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="5:5">
       <c r="E257"/>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="5:5">
       <c r="E258"/>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="5:5">
       <c r="E259"/>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="5:5">
       <c r="E260"/>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="5:5">
       <c r="E261"/>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="5:5">
       <c r="E262"/>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="5:5">
       <c r="E263"/>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="5:5">
       <c r="E264"/>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="5:5">
       <c r="E265"/>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="5:5">
       <c r="E266"/>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="5:5">
       <c r="E267"/>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="5:5">
       <c r="E268"/>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="5:5">
       <c r="E269"/>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="5:5">
       <c r="E270"/>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="5:5">
       <c r="E271"/>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="5:5">
       <c r="E272"/>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="5:5">
       <c r="E273"/>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="5:5">
       <c r="E274"/>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="5:5">
       <c r="E275"/>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="5:5">
       <c r="E276"/>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="5:5">
       <c r="E277"/>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="5:5">
       <c r="E278"/>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="5:5">
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -13983,7 +13987,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDFCCAD-07F9-4768-B22C-3C9115DDA520}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A310A2F1-830A-4EA7-8D0D-88880BC2A600}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027CD9AB-D23C-4A86-8D66-42EF95B9235C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1346,11 +1346,20 @@
       <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="36">
+        <v>561365</v>
+      </c>
       <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
+      <c r="E23" s="40">
+        <v>91.5</v>
+      </c>
+      <c r="F23" s="40">
+        <f>1998</f>
+        <v>1998</v>
+      </c>
+      <c r="G23" s="40">
+        <v>50</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -1828,7 +1837,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3049784</v>
+        <v>3611149</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -1836,15 +1845,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1406.25</v>
+        <v>1497.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>12720</v>
+        <v>14718</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -5753,9 +5762,13 @@
       <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="36">
+        <v>279612</v>
+      </c>
       <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
+      <c r="E23" s="40">
+        <v>148.5</v>
+      </c>
       <c r="F23" s="35"/>
       <c r="G23" s="35"/>
       <c r="H23" s="1"/>
@@ -6235,7 +6248,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2833771.0833333335</v>
+        <v>3113383.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -6243,7 +6256,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>620.41999999999996</v>
+        <v>768.92</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10165,10 +10178,16 @@
       <c r="B23" s="30">
         <v>46095</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="36">
+        <v>267902</v>
+      </c>
       <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
+      <c r="E23" s="35">
+        <v>193.25</v>
+      </c>
+      <c r="F23" s="35">
+        <v>1266</v>
+      </c>
       <c r="G23" s="35"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -10647,7 +10666,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2841472</v>
+        <v>3109374</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10655,11 +10674,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1960</v>
+        <v>2153.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>13680</v>
+        <v>14946</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027CD9AB-D23C-4A86-8D66-42EF95B9235C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080531F3-DE1C-458C-B515-445C20E19C83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="19">
   <si>
     <t>SALES</t>
   </si>
@@ -1405,11 +1405,13 @@
       <c r="B25" s="30">
         <v>46097</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11"/>
+      <c r="C25" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="7"/>
@@ -5160,7 +5162,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -5168,6 +5170,7 @@
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5565,7 +5568,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="35"/>
-      <c r="F16" s="35">
+      <c r="F16" s="40">
         <v>1200</v>
       </c>
       <c r="G16" s="35"/>
@@ -5816,10 +5819,16 @@
       <c r="B25" s="30">
         <v>46097</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="15"/>
+      <c r="C25" s="12">
+        <v>451583</v>
+      </c>
+      <c r="D25" s="15">
+        <v>158.5</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="12">
+        <v>2982</v>
+      </c>
       <c r="G25" s="11"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -6248,11 +6257,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3113383.0833333335</v>
+        <v>3564966.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>5746</v>
+        <v>5904.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6260,7 +6269,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>14394</v>
+        <v>17376</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10185,7 +10194,7 @@
       <c r="E23" s="35">
         <v>193.25</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="40">
         <v>1266</v>
       </c>
       <c r="G23" s="35"/>
@@ -10234,11 +10243,19 @@
       <c r="B25" s="30">
         <v>46097</v>
       </c>
-      <c r="C25" s="12"/>
+      <c r="C25" s="12">
+        <v>415764</v>
+      </c>
       <c r="D25" s="15"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11"/>
+      <c r="E25" s="12">
+        <v>691</v>
+      </c>
+      <c r="F25" s="12">
+        <v>1662</v>
+      </c>
+      <c r="G25" s="40">
+        <v>50</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="7"/>
@@ -10666,7 +10683,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3109374</v>
+        <v>3525138</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10674,15 +10691,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>2153.25</v>
+        <v>2844.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>14946</v>
+        <v>16608</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080531F3-DE1C-458C-B515-445C20E19C83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361326A8-15AC-47FD-8C88-550B18BDB7A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1431,10 +1431,16 @@
       <c r="B26" s="30">
         <v>46098</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="35"/>
+      <c r="C26" s="12">
+        <v>793392</v>
+      </c>
+      <c r="D26" s="35">
+        <v>874.75</v>
+      </c>
       <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="F26" s="36">
+        <v>5466</v>
+      </c>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1839,11 +1845,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3611149</v>
+        <v>4404541</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>3726</v>
+        <v>4600.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1851,7 +1857,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>14718</v>
+        <v>20184</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5849,10 +5855,16 @@
       <c r="B26" s="30">
         <v>46098</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="35"/>
+      <c r="C26" s="12">
+        <v>327138</v>
+      </c>
+      <c r="D26" s="35">
+        <v>1542</v>
+      </c>
       <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="F26" s="36">
+        <v>2496</v>
+      </c>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -6257,11 +6269,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3564966.0833333335</v>
+        <v>3892104.0833333335</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>5904.5</v>
+        <v>7446.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6269,7 +6281,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>17376</v>
+        <v>19872</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10275,8 +10287,12 @@
       <c r="B26" s="30">
         <v>46098</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="35"/>
+      <c r="C26" s="12">
+        <v>454572</v>
+      </c>
+      <c r="D26" s="35">
+        <v>242.75</v>
+      </c>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
       <c r="G26" s="11"/>
@@ -10683,11 +10699,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3525138</v>
+        <v>3979710</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>875.5</v>
+        <v>1118.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361326A8-15AC-47FD-8C88-550B18BDB7A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD22639-395A-4BDD-B2D3-218EE347FEE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1461,8 +1461,12 @@
       <c r="B27" s="30">
         <v>46099</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="35"/>
+      <c r="C27" s="12">
+        <v>401678</v>
+      </c>
+      <c r="D27" s="35">
+        <v>560.5</v>
+      </c>
       <c r="E27" s="36"/>
       <c r="F27" s="36"/>
       <c r="G27" s="11"/>
@@ -1845,11 +1849,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4404541</v>
+        <v>4806219</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>4600.75</v>
+        <v>5161.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5885,10 +5889,16 @@
       <c r="B27" s="30">
         <v>46099</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="35"/>
+      <c r="C27" s="12">
+        <v>309448</v>
+      </c>
+      <c r="D27" s="35">
+        <v>278.75</v>
+      </c>
       <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="F27" s="36">
+        <v>1944</v>
+      </c>
       <c r="G27" s="11"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -6269,11 +6279,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3892104.0833333335</v>
+        <v>4201552.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>7446.5</v>
+        <v>7725.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6281,7 +6291,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>19872</v>
+        <v>21816</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10315,11 +10325,20 @@
       <c r="B27" s="30">
         <v>46099</v>
       </c>
-      <c r="C27" s="12"/>
+      <c r="C27" s="12">
+        <v>311662</v>
+      </c>
       <c r="D27" s="35"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="11"/>
+      <c r="E27" s="36">
+        <v>261</v>
+      </c>
+      <c r="F27" s="36">
+        <f>1206</f>
+        <v>1206</v>
+      </c>
+      <c r="G27" s="40">
+        <v>70</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="7"/>
@@ -10699,7 +10718,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3979710</v>
+        <v>4291372</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10707,15 +10726,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>2844.25</v>
+        <v>3105.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>16608</v>
+        <v>17814</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD22639-395A-4BDD-B2D3-218EE347FEE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4E3EE4-975C-43D5-9037-7E2062D29401}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="19">
   <si>
     <t>SALES</t>
   </si>
@@ -1489,11 +1489,19 @@
       <c r="B28" s="30">
         <v>46100</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="12">
+        <v>449433</v>
+      </c>
+      <c r="D28" s="13">
+        <v>83</v>
+      </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="34"/>
+      <c r="F28" s="39">
+        <v>1944</v>
+      </c>
+      <c r="G28" s="33">
+        <v>50</v>
+      </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -1513,11 +1521,17 @@
       <c r="B29" s="30">
         <v>46101</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="12">
+        <v>343569</v>
+      </c>
+      <c r="D29" s="15">
+        <v>3750</v>
+      </c>
       <c r="E29" s="12"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="33"/>
+      <c r="G29" s="33">
+        <v>50</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -1537,11 +1551,13 @@
       <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="35"/>
+      <c r="C30" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -1849,11 +1865,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4806219</v>
+        <v>5599221</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>5161.25</v>
+        <v>8994.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1861,11 +1877,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>20184</v>
+        <v>22128</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -5172,7 +5188,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -5181,6 +5197,7 @@
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5919,10 +5936,16 @@
       <c r="B28" s="30">
         <v>46100</v>
       </c>
-      <c r="C28" s="12"/>
+      <c r="C28" s="12">
+        <v>267889</v>
+      </c>
       <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="39"/>
+      <c r="E28" s="12">
+        <v>22.25</v>
+      </c>
+      <c r="F28" s="39">
+        <v>624</v>
+      </c>
       <c r="G28" s="34"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -5943,10 +5966,16 @@
       <c r="B29" s="30">
         <v>46101</v>
       </c>
-      <c r="C29" s="12"/>
+      <c r="C29" s="12">
+        <v>348180</v>
+      </c>
       <c r="D29" s="15"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="39"/>
+      <c r="E29" s="12">
+        <v>352.75</v>
+      </c>
+      <c r="F29" s="39">
+        <v>648</v>
+      </c>
       <c r="G29" s="33"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -5967,11 +5996,13 @@
       <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="35"/>
+      <c r="C30" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -6279,7 +6310,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4201552.083333334</v>
+        <v>4817621.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -6287,11 +6318,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>768.92</v>
+        <v>1143.92</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>21816</v>
+        <v>23088</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -9602,7 +9633,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -9610,6 +9641,7 @@
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10358,10 +10390,16 @@
       <c r="B28" s="30">
         <v>46100</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="12">
+        <v>432743</v>
+      </c>
+      <c r="D28" s="13">
+        <v>422</v>
+      </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="39"/>
+      <c r="F28" s="39">
+        <v>3228</v>
+      </c>
       <c r="G28" s="34"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -10382,11 +10420,19 @@
       <c r="B29" s="30">
         <v>46101</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="12">
+        <v>313665</v>
+      </c>
+      <c r="D29" s="15">
+        <v>95</v>
+      </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="33"/>
+      <c r="F29" s="39">
+        <v>2052</v>
+      </c>
+      <c r="G29" s="33">
+        <v>50</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -10406,11 +10452,13 @@
       <c r="B30" s="30">
         <v>46102</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="35"/>
+      <c r="C30" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -10718,11 +10766,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4291372</v>
+        <v>5037780</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>1118.25</v>
+        <v>1635.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10730,11 +10778,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>17814</v>
+        <v>23094</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -14041,7 +14089,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -14049,6 +14097,7 @@
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4E3EE4-975C-43D5-9037-7E2062D29401}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA14F49D-724D-47C9-BFD3-FE023C870EFA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1603,8 +1603,12 @@
       <c r="B32" s="30">
         <v>46104</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="15"/>
+      <c r="C32" s="12">
+        <v>441683</v>
+      </c>
+      <c r="D32" s="15">
+        <v>479.25</v>
+      </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
       <c r="G32" s="11"/>
@@ -1865,11 +1869,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5599221</v>
+        <v>6040904</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>8994.25</v>
+        <v>9473.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6048,10 +6052,16 @@
       <c r="B32" s="30">
         <v>46104</v>
       </c>
-      <c r="C32" s="12"/>
+      <c r="C32" s="12">
+        <v>356198</v>
+      </c>
       <c r="D32" s="15"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="E32" s="12">
+        <v>245</v>
+      </c>
+      <c r="F32" s="12">
+        <v>2598</v>
+      </c>
       <c r="G32" s="11"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6310,7 +6320,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4817621.083333334</v>
+        <v>5173819.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -6318,11 +6328,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1143.92</v>
+        <v>1388.92</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>23088</v>
+        <v>25686</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10504,10 +10514,16 @@
       <c r="B32" s="30">
         <v>46104</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="15"/>
+      <c r="C32" s="12">
+        <v>376448</v>
+      </c>
+      <c r="D32" s="15">
+        <v>79.5</v>
+      </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="12">
+        <v>2304</v>
+      </c>
       <c r="G32" s="11"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -10766,11 +10782,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5037780</v>
+        <v>5414228</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>1635.25</v>
+        <v>1714.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10778,7 +10794,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>23094</v>
+        <v>25398</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA14F49D-724D-47C9-BFD3-FE023C870EFA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D230F8-7D97-4E99-A823-57C0B42311E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -123,9 +123,6 @@
       </rPr>
       <t xml:space="preserve"> PORMENTO, ESTEMARK</t>
     </r>
-  </si>
-  <si>
-    <t>FEBRUARY</t>
   </si>
   <si>
     <t>MARCH</t>
@@ -829,7 +826,7 @@
     <row r="4" spans="1:18" ht="15.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="1"/>
@@ -951,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>5</v>
@@ -1120,7 +1117,7 @@
         <v>46087</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -1321,7 +1318,7 @@
         <v>46094</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -1406,7 +1403,7 @@
         <v>46097</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="42"/>
@@ -1552,7 +1549,7 @@
         <v>46102</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
@@ -5394,7 +5391,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>5</v>
@@ -5567,7 +5564,7 @@
         <v>46087</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5771,7 +5768,7 @@
         <v>46094</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -6001,7 +5998,7 @@
         <v>46102</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
@@ -9844,7 +9841,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>5</v>
@@ -9989,7 +9986,7 @@
         <v>46086</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42"/>
@@ -10226,7 +10223,7 @@
         <v>46094</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -10463,7 +10460,7 @@
         <v>46102</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D230F8-7D97-4E99-A823-57C0B42311E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C63E8E-0C00-4F8F-B0B5-76B9CD4E049A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1628,10 +1628,16 @@
       <c r="B33" s="30">
         <v>46105</v>
       </c>
-      <c r="C33" s="12"/>
+      <c r="C33" s="12">
+        <v>356654</v>
+      </c>
       <c r="D33" s="35"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
+      <c r="E33" s="34">
+        <v>164.5</v>
+      </c>
+      <c r="F33" s="33">
+        <v>2592</v>
+      </c>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1866,7 +1872,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6040904</v>
+        <v>6397558</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -1874,11 +1880,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1497.75</v>
+        <v>1662.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>22128</v>
+        <v>24720</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -6079,10 +6085,16 @@
       <c r="B33" s="30">
         <v>46105</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="35"/>
+      <c r="C33" s="12">
+        <v>291721</v>
+      </c>
+      <c r="D33" s="35">
+        <v>375.25</v>
+      </c>
       <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
+      <c r="F33" s="33">
+        <v>2064</v>
+      </c>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6317,11 +6329,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5173819.083333334</v>
+        <v>5465540.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>7725.25</v>
+        <v>8100.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6329,7 +6341,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>25686</v>
+        <v>27750</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10541,8 +10553,12 @@
       <c r="B33" s="30">
         <v>46105</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="35"/>
+      <c r="C33" s="12">
+        <v>362847</v>
+      </c>
+      <c r="D33" s="35">
+        <v>103.25</v>
+      </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34"/>
       <c r="G33" s="11"/>
@@ -10779,11 +10795,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5414228</v>
+        <v>5777075</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>1714.75</v>
+        <v>1818</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C63E8E-0C00-4F8F-B0B5-76B9CD4E049A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820D7B6C-1418-4A1D-9A38-5BF5718656EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -1658,11 +1658,13 @@
       <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
+      <c r="C34" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -5195,7 +5197,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -5205,6 +5207,7 @@
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6115,10 +6118,16 @@
       <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
+      <c r="C34" s="40">
+        <v>232411</v>
+      </c>
+      <c r="D34" s="35">
+        <v>340.75</v>
+      </c>
       <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
+      <c r="F34" s="40">
+        <v>1296</v>
+      </c>
       <c r="G34" s="35"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6329,11 +6338,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5465540.083333334</v>
+        <v>5697951.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>8100.5</v>
+        <v>8441.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6341,7 +6350,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>27750</v>
+        <v>29046</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10264,7 +10273,7 @@
         <v>267902</v>
       </c>
       <c r="D23" s="35"/>
-      <c r="E23" s="35">
+      <c r="E23" s="40">
         <v>193.25</v>
       </c>
       <c r="F23" s="40">
@@ -10581,11 +10590,20 @@
       <c r="B34" s="30">
         <v>46106</v>
       </c>
-      <c r="C34" s="35"/>
+      <c r="C34" s="40">
+        <v>429981</v>
+      </c>
       <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
+      <c r="E34" s="40">
+        <v>36.75</v>
+      </c>
+      <c r="F34" s="40">
+        <f>1620+10*6</f>
+        <v>1680</v>
+      </c>
+      <c r="G34" s="40">
+        <v>50</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -10795,7 +10813,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5777075</v>
+        <v>6207056</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10803,15 +10821,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>3105.25</v>
+        <v>3142</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>25398</v>
+        <v>27078</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820D7B6C-1418-4A1D-9A38-5BF5718656EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9E4C92-52BB-4D92-94F5-39C5932346F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -1684,11 +1684,17 @@
       <c r="B35" s="30">
         <v>46107</v>
       </c>
-      <c r="C35" s="12"/>
+      <c r="C35" s="12">
+        <v>441829</v>
+      </c>
       <c r="D35" s="13"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="34"/>
+      <c r="E35" s="12">
+        <v>53</v>
+      </c>
+      <c r="F35" s="39">
+        <v>2886</v>
+      </c>
+      <c r="G35" s="37"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -1874,7 +1880,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6397558</v>
+        <v>6839387</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -1882,11 +1888,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1662.25</v>
+        <v>1715.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>24720</v>
+        <v>27606</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -6148,10 +6154,16 @@
       <c r="B35" s="30">
         <v>46107</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="12">
+        <v>255036</v>
+      </c>
+      <c r="D35" s="13">
+        <v>682.5</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="39"/>
+      <c r="F35" s="39">
+        <v>1296</v>
+      </c>
       <c r="G35" s="34"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6338,11 +6350,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5697951.083333334</v>
+        <v>5952987.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>8441.25</v>
+        <v>9123.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6350,7 +6362,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>29046</v>
+        <v>30342</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10623,11 +10635,13 @@
       <c r="B35" s="30">
         <v>46107</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="34"/>
+      <c r="C35" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="43"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -14136,7 +14150,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -14145,6 +14159,7 @@
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C35:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9E4C92-52BB-4D92-94F5-39C5932346F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA70726-7A17-4EEF-B7B8-EC2B471DD6D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1714,11 +1714,17 @@
       <c r="B36" s="30">
         <v>46108</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="12">
+        <v>236341</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1490.75</v>
+      </c>
       <c r="E36" s="12"/>
       <c r="F36" s="39"/>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33">
+        <v>50</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -1880,11 +1886,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6839387</v>
+        <v>7075728</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>9473.5</v>
+        <v>10964.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1896,7 +1902,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -6184,10 +6190,16 @@
       <c r="B36" s="30">
         <v>46108</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="12">
+        <v>377865</v>
+      </c>
+      <c r="D36" s="13">
+        <v>76</v>
+      </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="39"/>
+      <c r="F36" s="39">
+        <v>1980</v>
+      </c>
       <c r="G36" s="34"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6350,11 +6362,11 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5952987.083333334</v>
+        <v>6330852.083333334</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>9123.75</v>
+        <v>9199.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -6362,7 +6374,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>30342</v>
+        <v>32322</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10661,11 +10673,19 @@
       <c r="B36" s="30">
         <v>46108</v>
       </c>
-      <c r="C36" s="12"/>
+      <c r="C36" s="12">
+        <v>488484</v>
+      </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="34"/>
+      <c r="E36" s="12">
+        <v>107.5</v>
+      </c>
+      <c r="F36" s="39">
+        <v>2568</v>
+      </c>
+      <c r="G36" s="33">
+        <v>50</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -10827,7 +10847,7 @@
       <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6207056</v>
+        <v>6695540</v>
       </c>
       <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
@@ -10835,15 +10855,15 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>3142</v>
+        <v>3249.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>27078</v>
+        <v>29646</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA70726-7A17-4EEF-B7B8-EC2B471DD6D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3878A510-668E-4A61-9DCB-FBE3BD61C79D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -351,7 +351,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -390,9 +390,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
@@ -969,16 +966,16 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -995,17 +992,17 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>265882</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>15.75</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="37">
+      <c r="E11" s="33"/>
+      <c r="F11" s="36">
         <v>1356</v>
       </c>
       <c r="G11" s="11"/>
@@ -1025,17 +1022,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
         <v>322724</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="38">
+      <c r="E12" s="37">
         <v>928.5</v>
       </c>
-      <c r="F12" s="38"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="11"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1053,20 +1050,20 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>46085</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="35">
         <v>387395</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="34">
         <v>836.75</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="36">
+      <c r="E13" s="34"/>
+      <c r="F13" s="35">
         <v>2004</v>
       </c>
-      <c r="G13" s="35"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1083,7 +1080,7 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>46086</v>
       </c>
       <c r="C14" s="12">
@@ -1096,7 +1093,7 @@
       <c r="F14" s="12">
         <v>1950</v>
       </c>
-      <c r="G14" s="35"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1113,16 +1110,16 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>46087</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1139,18 +1136,18 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>46088</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="35">
         <v>319434</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <v>1647.25</v>
       </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1167,16 +1164,16 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1193,7 +1190,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>46090</v>
       </c>
       <c r="C18" s="12">
@@ -1224,17 +1221,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>46091</v>
       </c>
       <c r="C19" s="12">
         <v>267570</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="37">
+      <c r="D19" s="34"/>
+      <c r="E19" s="36">
         <v>477.75</v>
       </c>
-      <c r="F19" s="37"/>
+      <c r="F19" s="36"/>
       <c r="G19" s="12">
         <v>50</v>
       </c>
@@ -1254,20 +1251,20 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>46092</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="35">
         <v>320439</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="34">
         <v>297</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="40">
+      <c r="E20" s="34"/>
+      <c r="F20" s="39">
         <v>1938</v>
       </c>
-      <c r="G20" s="35"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1284,7 +1281,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>46093</v>
       </c>
       <c r="C21" s="12">
@@ -1294,10 +1291,10 @@
         <v>178.5</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="39">
+      <c r="F21" s="38">
         <v>2268</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1314,16 +1311,16 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>46094</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1340,21 +1337,21 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>46095</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="35">
         <v>561365</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="40">
+      <c r="D23" s="34"/>
+      <c r="E23" s="39">
         <v>91.5</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="39">
         <f>1998</f>
         <v>1998</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="39">
         <v>50</v>
       </c>
       <c r="H23" s="1"/>
@@ -1373,16 +1370,16 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -1399,16 +1396,16 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>46097</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="7"/>
@@ -1425,17 +1422,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>46098</v>
       </c>
       <c r="C26" s="12">
         <v>793392</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="34">
         <v>874.75</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36">
+      <c r="E26" s="35"/>
+      <c r="F26" s="35">
         <v>5466</v>
       </c>
       <c r="G26" s="11"/>
@@ -1455,17 +1452,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>46099</v>
       </c>
       <c r="C27" s="12">
         <v>401678</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="34">
         <v>560.5</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="11"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1483,7 +1480,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>46100</v>
       </c>
       <c r="C28" s="12">
@@ -1493,10 +1490,10 @@
         <v>83</v>
       </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="39">
+      <c r="F28" s="38">
         <v>1944</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="32">
         <v>50</v>
       </c>
       <c r="H28" s="1"/>
@@ -1515,7 +1512,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>46101</v>
       </c>
       <c r="C29" s="12">
@@ -1525,8 +1522,8 @@
         <v>3750</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="33">
+      <c r="F29" s="38"/>
+      <c r="G29" s="32">
         <v>50</v>
       </c>
       <c r="H29" s="1"/>
@@ -1545,16 +1542,16 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>46102</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -1571,16 +1568,16 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -1597,7 +1594,7 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>46104</v>
       </c>
       <c r="C32" s="12">
@@ -1625,17 +1622,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>46105</v>
       </c>
       <c r="C33" s="12">
         <v>356654</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="34">
+      <c r="D33" s="34"/>
+      <c r="E33" s="33">
         <v>164.5</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="32">
         <v>2592</v>
       </c>
       <c r="G33" s="11"/>
@@ -1655,16 +1652,16 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>46106</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="43"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -1681,7 +1678,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>46107</v>
       </c>
       <c r="C35" s="12">
@@ -1691,10 +1688,10 @@
       <c r="E35" s="12">
         <v>53</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="38">
         <v>2886</v>
       </c>
-      <c r="G35" s="37"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -1711,7 +1708,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>46108</v>
       </c>
       <c r="C36" s="12">
@@ -1721,8 +1718,8 @@
         <v>1490.75</v>
       </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="33">
+      <c r="F36" s="38"/>
+      <c r="G36" s="32">
         <v>50</v>
       </c>
       <c r="H36" s="1"/>
@@ -1741,14 +1738,16 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>46109</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="33"/>
+      <c r="C37" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -1765,16 +1764,16 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -1791,13 +1790,19 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>46111</v>
       </c>
-      <c r="C39" s="12"/>
+      <c r="C39" s="12">
+        <v>712160</v>
+      </c>
       <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+      <c r="E39" s="12">
+        <v>1676.5</v>
+      </c>
+      <c r="F39" s="12">
+        <v>5202</v>
+      </c>
       <c r="G39" s="11"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1815,7 +1820,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -1839,11 +1844,11 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1861,7 +1866,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="30"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -1880,25 +1885,25 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="30"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7075728</v>
-      </c>
-      <c r="D43" s="31">
+        <v>7787888</v>
+      </c>
+      <c r="D43" s="30">
         <f>SUM(D10:D42)</f>
         <v>10964.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1715.25</v>
+        <v>3391.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>27606</v>
+        <v>32808</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -1918,9 +1923,9 @@
     </row>
     <row r="44" spans="1:18" ht="15">
       <c r="A44" s="1"/>
-      <c r="B44" s="32"/>
+      <c r="B44" s="31"/>
       <c r="C44" s="22"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="26"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="1"/>
@@ -5209,7 +5214,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -5220,6 +5225,7 @@
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5433,16 +5439,16 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -5459,17 +5465,17 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>313708.5</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>624</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="37">
+      <c r="E11" s="33"/>
+      <c r="F11" s="36">
         <v>1380</v>
       </c>
       <c r="G11" s="11"/>
@@ -5489,7 +5495,7 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
@@ -5499,7 +5505,7 @@
         <v>142</v>
       </c>
       <c r="E12" s="13"/>
-      <c r="F12" s="38">
+      <c r="F12" s="37">
         <v>732</v>
       </c>
       <c r="G12" s="11"/>
@@ -5519,20 +5525,20 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>46085</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="35">
         <v>253739</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="34">
         <v>44</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="36">
+      <c r="E13" s="34"/>
+      <c r="F13" s="35">
         <v>1944</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <v>50</v>
       </c>
       <c r="H13" s="1"/>
@@ -5551,7 +5557,7 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>46086</v>
       </c>
       <c r="C14" s="12">
@@ -5564,7 +5570,7 @@
       <c r="F14" s="12">
         <v>1182</v>
       </c>
-      <c r="G14" s="35"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -5581,16 +5587,16 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>46087</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -5607,20 +5613,20 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>46088</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="35">
         <v>351657</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <v>12</v>
       </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="40">
+      <c r="E16" s="34"/>
+      <c r="F16" s="39">
         <v>1200</v>
       </c>
-      <c r="G16" s="35"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -5637,16 +5643,16 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -5663,7 +5669,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>46090</v>
       </c>
       <c r="C18" s="12">
@@ -5693,17 +5699,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>46091</v>
       </c>
       <c r="C19" s="12">
         <v>266386.58333333331</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="37">
+      <c r="D19" s="34"/>
+      <c r="E19" s="36">
         <v>39.92</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="36">
         <v>648</v>
       </c>
       <c r="G19" s="11"/>
@@ -5723,20 +5729,20 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>46092</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="35">
         <v>268786</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="34">
         <v>1173.5</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="40">
+      <c r="E20" s="34"/>
+      <c r="F20" s="39">
         <v>1776</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="39">
         <v>50</v>
       </c>
       <c r="H20" s="1"/>
@@ -5755,7 +5761,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>46093</v>
       </c>
       <c r="C21" s="12">
@@ -5765,10 +5771,10 @@
       <c r="E21" s="12">
         <v>580.5</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="38">
         <v>2160</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -5785,16 +5791,16 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>46094</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5811,18 +5817,18 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>46095</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="35">
         <v>279612</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="40">
+      <c r="D23" s="34"/>
+      <c r="E23" s="39">
         <v>148.5</v>
       </c>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -5839,16 +5845,16 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -5865,7 +5871,7 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>46097</v>
       </c>
       <c r="C25" s="12">
@@ -5895,17 +5901,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>46098</v>
       </c>
       <c r="C26" s="12">
         <v>327138</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="34">
         <v>1542</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36">
+      <c r="E26" s="35"/>
+      <c r="F26" s="35">
         <v>2496</v>
       </c>
       <c r="G26" s="11"/>
@@ -5925,17 +5931,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>46099</v>
       </c>
       <c r="C27" s="12">
         <v>309448</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="34">
         <v>278.75</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36">
+      <c r="E27" s="35"/>
+      <c r="F27" s="35">
         <v>1944</v>
       </c>
       <c r="G27" s="11"/>
@@ -5955,7 +5961,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>46100</v>
       </c>
       <c r="C28" s="12">
@@ -5965,10 +5971,10 @@
       <c r="E28" s="12">
         <v>22.25</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="38">
         <v>624</v>
       </c>
-      <c r="G28" s="34"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -5985,7 +5991,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>46101</v>
       </c>
       <c r="C29" s="12">
@@ -5995,10 +6001,10 @@
       <c r="E29" s="12">
         <v>352.75</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F29" s="38">
         <v>648</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="7"/>
@@ -6015,16 +6021,16 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>46102</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -6041,16 +6047,16 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -6067,7 +6073,7 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>46104</v>
       </c>
       <c r="C32" s="12">
@@ -6097,17 +6103,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>46105</v>
       </c>
       <c r="C33" s="12">
         <v>291721</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="34">
         <v>375.25</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="33">
+      <c r="E33" s="33"/>
+      <c r="F33" s="32">
         <v>2064</v>
       </c>
       <c r="G33" s="11"/>
@@ -6127,20 +6133,20 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>46106</v>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="39">
         <v>232411</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="34">
         <v>340.75</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="40">
+      <c r="E34" s="34"/>
+      <c r="F34" s="39">
         <v>1296</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="7"/>
@@ -6157,7 +6163,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>46107</v>
       </c>
       <c r="C35" s="12">
@@ -6167,10 +6173,10 @@
         <v>682.5</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="39">
+      <c r="F35" s="38">
         <v>1296</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -6187,7 +6193,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>46108</v>
       </c>
       <c r="C36" s="12">
@@ -6197,10 +6203,10 @@
         <v>76</v>
       </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="39">
+      <c r="F36" s="38">
         <v>1980</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="7"/>
@@ -6217,14 +6223,16 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>46109</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="33"/>
+      <c r="C37" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -6241,16 +6249,16 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -6267,14 +6275,16 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>46111</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="11"/>
+      <c r="C39" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="42"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="7"/>
@@ -6291,7 +6301,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -6315,11 +6325,11 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -6337,7 +6347,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="30"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -6356,15 +6366,15 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="30"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
         <v>6330852.083333334</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <f>SUM(D10:D42)</f>
         <v>9199.75</v>
       </c>
@@ -6396,7 +6406,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="26"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="1"/>
@@ -9685,7 +9695,8 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -9694,6 +9705,7 @@
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9907,16 +9919,16 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -9933,20 +9945,20 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>46083</v>
       </c>
       <c r="C11" s="12">
         <v>259606</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="37">
+      <c r="D11" s="34"/>
+      <c r="E11" s="36">
         <v>107</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="36">
         <v>690</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <v>50</v>
       </c>
       <c r="H11" s="1"/>
@@ -9965,17 +9977,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>46084</v>
       </c>
       <c r="C12" s="12">
         <v>273403</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="38">
+      <c r="E12" s="37">
         <v>1.5</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="37">
         <v>918</v>
       </c>
       <c r="G12" s="11"/>
@@ -9995,20 +10007,20 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>46085</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="35">
         <v>236285</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="34">
         <v>67.75</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="36">
+      <c r="E13" s="34"/>
+      <c r="F13" s="35">
         <v>1158</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <v>50</v>
       </c>
       <c r="H13" s="1"/>
@@ -10027,16 +10039,16 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>46086</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -10053,7 +10065,7 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>46087</v>
       </c>
       <c r="C15" s="12">
@@ -10063,11 +10075,11 @@
       <c r="E15" s="12">
         <v>393</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="38">
         <f>2472</f>
         <v>2472</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="32">
         <v>50</v>
       </c>
       <c r="H15" s="1"/>
@@ -10086,20 +10098,20 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>46088</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="35">
         <v>412474</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36">
+      <c r="D16" s="34"/>
+      <c r="E16" s="35">
         <v>1346.5</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="35">
         <v>2736</v>
       </c>
-      <c r="G16" s="35"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -10116,16 +10128,16 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -10142,7 +10154,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>46090</v>
       </c>
       <c r="C18" s="12">
@@ -10172,17 +10184,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>46091</v>
       </c>
       <c r="C19" s="12">
         <v>281186</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <v>149.75</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37">
+      <c r="E19" s="36"/>
+      <c r="F19" s="36">
         <v>1128</v>
       </c>
       <c r="G19" s="11"/>
@@ -10202,20 +10214,20 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>46092</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="35">
         <v>349583</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="40">
+      <c r="D20" s="34"/>
+      <c r="E20" s="39">
         <v>112</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="39">
         <v>2388</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="39">
         <v>50</v>
       </c>
       <c r="H20" s="1"/>
@@ -10234,7 +10246,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>46093</v>
       </c>
       <c r="C21" s="12">
@@ -10244,10 +10256,10 @@
         <v>437.25</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="39">
+      <c r="F21" s="38">
         <v>1890</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -10264,16 +10276,16 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>46094</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -10290,20 +10302,20 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>46095</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="35">
         <v>267902</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="40">
+      <c r="D23" s="34"/>
+      <c r="E23" s="39">
         <v>193.25</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="39">
         <v>1266</v>
       </c>
-      <c r="G23" s="35"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="7"/>
@@ -10320,16 +10332,16 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="7"/>
@@ -10346,7 +10358,7 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>46097</v>
       </c>
       <c r="C25" s="12">
@@ -10359,7 +10371,7 @@
       <c r="F25" s="12">
         <v>1662</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="39">
         <v>50</v>
       </c>
       <c r="H25" s="1"/>
@@ -10378,17 +10390,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>46098</v>
       </c>
       <c r="C26" s="12">
         <v>454572</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="34">
         <v>242.75</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="11"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -10406,21 +10418,21 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>46099</v>
       </c>
       <c r="C27" s="12">
         <v>311662</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="E27" s="36">
+      <c r="D27" s="34"/>
+      <c r="E27" s="35">
         <v>261</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="35">
         <f>1206</f>
         <v>1206</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="39">
         <v>70</v>
       </c>
       <c r="H27" s="1"/>
@@ -10439,7 +10451,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>46100</v>
       </c>
       <c r="C28" s="12">
@@ -10449,10 +10461,10 @@
         <v>422</v>
       </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="39">
+      <c r="F28" s="38">
         <v>3228</v>
       </c>
-      <c r="G28" s="34"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="7"/>
@@ -10469,7 +10481,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>46101</v>
       </c>
       <c r="C29" s="12">
@@ -10479,10 +10491,10 @@
         <v>95</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="39">
+      <c r="F29" s="38">
         <v>2052</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="32">
         <v>50</v>
       </c>
       <c r="H29" s="1"/>
@@ -10501,16 +10513,16 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>46102</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="7"/>
@@ -10527,16 +10539,16 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="19"/>
@@ -10553,7 +10565,7 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>46104</v>
       </c>
       <c r="C32" s="12">
@@ -10583,17 +10595,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>46105</v>
       </c>
       <c r="C33" s="12">
         <v>362847</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="34">
         <v>103.25</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -10611,21 +10623,21 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>46106</v>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="39">
         <v>429981</v>
       </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="40">
+      <c r="D34" s="34"/>
+      <c r="E34" s="39">
         <v>36.75</v>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="39">
         <f>1620+10*6</f>
         <v>1680</v>
       </c>
-      <c r="G34" s="40">
+      <c r="G34" s="39">
         <v>50</v>
       </c>
       <c r="H34" s="1"/>
@@ -10644,16 +10656,16 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>46107</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="43"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="42"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="7"/>
@@ -10670,7 +10682,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>46108</v>
       </c>
       <c r="C36" s="12">
@@ -10680,10 +10692,10 @@
       <c r="E36" s="12">
         <v>107.5</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="38">
         <v>2568</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="32">
         <v>50</v>
       </c>
       <c r="H36" s="1"/>
@@ -10702,14 +10714,16 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>46109</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="33"/>
+      <c r="C37" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="8"/>
@@ -10726,16 +10740,16 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="7"/>
@@ -10752,13 +10766,19 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>46111</v>
       </c>
-      <c r="C39" s="12"/>
+      <c r="C39" s="12">
+        <v>384352</v>
+      </c>
       <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+      <c r="E39" s="12">
+        <v>148.25</v>
+      </c>
+      <c r="F39" s="12">
+        <v>2316</v>
+      </c>
       <c r="G39" s="11"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -10776,7 +10796,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>46112</v>
       </c>
       <c r="C40" s="12"/>
@@ -10800,11 +10820,11 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="11"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -10822,7 +10842,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="30"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -10841,25 +10861,25 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="30"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6695540</v>
-      </c>
-      <c r="D43" s="31">
+        <v>7079892</v>
+      </c>
+      <c r="D43" s="30">
         <f>SUM(D10:D42)</f>
         <v>1818</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>3249.5</v>
+        <v>3397.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>29646</v>
+        <v>31962</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10881,7 +10901,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="26"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="1"/>
@@ -14170,7 +14190,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>
@@ -14180,6 +14200,7 @@
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3878A510-668E-4A61-9DCB-FBE3BD61C79D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB41EF1-976E-410A-B5FE-48CD1DA5351E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MARCH, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -1823,10 +1823,16 @@
       <c r="B40" s="29">
         <v>46112</v>
       </c>
-      <c r="C40" s="12"/>
+      <c r="C40" s="12">
+        <v>724297</v>
+      </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="E40" s="12">
+        <v>413.25</v>
+      </c>
+      <c r="F40" s="12">
+        <v>7968</v>
+      </c>
       <c r="G40" s="11"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1891,7 +1897,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7787888</v>
+        <v>8512185</v>
       </c>
       <c r="D43" s="30">
         <f>SUM(D10:D42)</f>
@@ -1899,11 +1905,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>3391.75</v>
+        <v>3805</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>32808</v>
+        <v>40776</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -6304,10 +6310,16 @@
       <c r="B40" s="29">
         <v>46112</v>
       </c>
-      <c r="C40" s="12"/>
+      <c r="C40" s="12">
+        <v>315369</v>
+      </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="E40" s="12">
+        <v>21</v>
+      </c>
+      <c r="F40" s="12">
+        <v>1200</v>
+      </c>
       <c r="G40" s="11"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -6372,7 +6384,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6330852.083333334</v>
+        <v>6646221.083333334</v>
       </c>
       <c r="D43" s="30">
         <f>SUM(D10:D42)</f>
@@ -6380,11 +6392,11 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1388.92</v>
+        <v>1409.92</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>32322</v>
+        <v>33522</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10799,11 +10811,13 @@
       <c r="B40" s="29">
         <v>46112</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="11"/>
+      <c r="C40" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="42"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="7"/>
@@ -14190,7 +14204,8 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="C40:G40"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C17:G17"/>

--- a/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SHORT OVER ALL ROUTES - MARCH 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB41EF1-976E-410A-B5FE-48CD1DA5351E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6024DF-A57A-4244-B27D-2131C4FABD2E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
